--- a/InputData/io-model/BPEaCP/cn-BAU Pop Employment and Compensation Projections.xlsx
+++ b/InputData/io-model/BPEaCP/cn-BAU Pop Employment and Compensation Projections.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlx6\Desktop\eps-china2019-smart-trans\InputData\io-model\BPEaCP\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AAA425-5D60-40F0-B97A-C27E7DED3684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView xWindow="28665" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="6" r:id="rId1"/>
@@ -18,12 +24,25 @@
   <externalReferences>
     <externalReference r:id="rId8"/>
   </externalReferences>
-  <calcPr calcId="144525" iterate="1" iterateCount="100" iterateDelta="1e-5"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
   <si>
     <t>BPEaCP BAU Population Employment and Compensation Projections</t>
   </si>
@@ -202,15 +221,6 @@
     <t>就业人数</t>
   </si>
   <si>
-    <t>2020年15-65岁人口数</t>
-  </si>
-  <si>
-    <t>2020年就业人口数</t>
-  </si>
-  <si>
-    <t>2020年就业比重</t>
-  </si>
-  <si>
     <t>平均GDP</t>
   </si>
   <si>
@@ -311,21 +321,33 @@
   </si>
   <si>
     <t>2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2019年15-65岁人口数</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2019年就业人口数</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2019年就业比重</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="0.0000_ "/>
+    <numFmt numFmtId="179" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,12 +360,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -351,6 +375,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -358,6 +383,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -366,6 +392,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -374,341 +401,35 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -716,275 +437,38 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -992,76 +476,51 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="10">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="超链接" xfId="2" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
@@ -1081,14 +540,14 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.13553937007874"/>
-          <c:y val="0.351689997083698"/>
-          <c:w val="0.808571741032371"/>
-          <c:h val="0.540910615339749"/>
+          <c:x val="0.13553937007874001"/>
+          <c:y val="0.35168999708369802"/>
+          <c:w val="0.80857174103237095"/>
+          <c:h val="0.54091061533974905"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
-        <c:scatterStyle val="marker"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1126,9 +585,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:trendline>
             <c:spPr>
               <a:ln w="19050" cap="rnd">
@@ -1146,8 +602,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.134023840769904"/>
-                  <c:y val="-0.384353674540682"/>
+                  <c:x val="0.13402384076990401"/>
+                  <c:y val="-0.38435367454068198"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="0.000000E+00" sourceLinked="0"/>
@@ -1175,6 +631,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="zh-CN"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -1228,30 +685,35 @@
                   <c:v>1422735306.02742</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1419485366.60866</c:v>
+                  <c:v>1419485366.608664</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1406477694.67206</c:v>
+                  <c:v>1406477694.6720653</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1385994440.2763</c:v>
+                  <c:v>1385994440.276305</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1360436211.92963</c:v>
+                  <c:v>1360436211.9296308</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1327783400.25489</c:v>
+                  <c:v>1327783400.2548852</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1284286657.36219</c:v>
+                  <c:v>1284286657.3621924</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1229815757.98823</c:v>
+                  <c:v>1229815757.9882255</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CC4B-4A1E-A291-329B072C5EC4}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1289,9 +751,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:trendline>
             <c:spPr>
               <a:ln w="19050" cap="rnd">
@@ -1310,7 +769,7 @@
               <c:layout>
                 <c:manualLayout>
                   <c:x val="0.1388156167979"/>
-                  <c:y val="-0.429966827063284"/>
+                  <c:y val="-0.42996682706328399"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="0.000000E+00" sourceLinked="0"/>
@@ -1338,6 +797,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="zh-CN"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -1388,33 +848,38 @@
                   <c:v>965759506</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>968859499.3732</c:v>
+                  <c:v>968859499.37319994</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>952096784.652617</c:v>
+                  <c:v>952096784.65261674</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>906520608.650105</c:v>
+                  <c:v>906520608.65010464</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>850677077.111454</c:v>
+                  <c:v>850677077.11145449</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>806380603.079528</c:v>
+                  <c:v>806380603.07952845</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>754947602.258881</c:v>
+                  <c:v>754947602.25888133</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>682022497.949468</c:v>
+                  <c:v>682022497.94946814</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>643001472.497549</c:v>
+                  <c:v>643001472.4975493</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-CC4B-4A1E-A291-329B072C5EC4}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1482,6 +947,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1845272128"/>
@@ -1543,6 +1009,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1845271712"/>
@@ -1583,6 +1050,7 @@
       <a:pPr>
         <a:defRPr lang="zh-CN"/>
       </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1594,7 +1062,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
@@ -1611,7 +1079,7 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="marker"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1638,9 +1106,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:trendline>
             <c:spPr>
               <a:ln w="19050" cap="rnd">
@@ -1656,7 +1121,7 @@
             <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
-              <c:layout/>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -1681,6 +1146,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="zh-CN"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -1692,34 +1158,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.177518826278889</c:v>
+                  <c:v>0.17751882627888871</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0963144692229236</c:v>
+                  <c:v>9.6314469222923638E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0936863543788187</c:v>
+                  <c:v>9.368635437881867E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0785111616893119</c:v>
+                  <c:v>7.8511161689311937E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0641626875852661</c:v>
+                  <c:v>6.4162687585266109E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0773406514162094</c:v>
+                  <c:v>7.7340651416209383E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.108008106650801</c:v>
+                  <c:v>0.10800810665080052</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0997113706537791</c:v>
+                  <c:v>9.9711370653779108E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0693380535294656</c:v>
+                  <c:v>6.9338053529465649E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.0249721738634094</c:v>
+                  <c:v>2.4972173863409441E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1731,39 +1197,44 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.143955773283341</c:v>
+                  <c:v>0.14395577328334119</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.118902366085313</c:v>
+                  <c:v>0.11890236608531302</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.100793260493062</c:v>
+                  <c:v>0.1007932604930617</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0947302993221064</c:v>
+                  <c:v>9.4730299322106415E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.100585521646558</c:v>
+                  <c:v>0.10058552164655787</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0893130632446113</c:v>
+                  <c:v>8.9313063244611302E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0998830824786514</c:v>
+                  <c:v>9.9883082478651408E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.10892381388089</c:v>
+                  <c:v>0.10892381388089012</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0981398565760256</c:v>
+                  <c:v>9.8139856576025641E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.0759991602302736</c:v>
+                  <c:v>7.5999160230273644E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9FF2-4A8B-908E-72BDBE022039}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1831,6 +1302,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="815059031"/>
@@ -1892,6 +1364,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="305586085"/>
@@ -1932,6 +1405,7 @@
       <a:pPr>
         <a:defRPr lang="zh-CN"/>
       </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3055,7 +2529,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
@@ -3069,14 +2543,20 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7853045" y="828675"/>
-        <a:ext cx="4905375" cy="2743200"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3090,7 +2570,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -3104,14 +2584,20 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>117475</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="图表 2"/>
+        <xdr:cNvPr id="3" name="图表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="139700" y="2803525"/>
-        <a:ext cx="4572000" cy="2743200"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3125,8 +2611,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="汇率"/>
       <sheetName val="Calculation"/>
@@ -3137,22 +2626,22 @@
       <sheetData sheetId="1">
         <row r="45">
           <cell r="L45">
-            <v>0.264027318393146</v>
+            <v>0.26402731839314603</v>
           </cell>
         </row>
         <row r="46">
           <cell r="L46">
-            <v>0.258730967526493</v>
+            <v>0.25873096752649299</v>
           </cell>
         </row>
         <row r="47">
           <cell r="L47">
-            <v>0.257182474220425</v>
+            <v>0.25718247422042501</v>
           </cell>
         </row>
         <row r="48">
           <cell r="L48">
-            <v>0.250657416210714</v>
+            <v>0.25065741621071402</v>
           </cell>
         </row>
         <row r="49">
@@ -3162,7 +2651,7 @@
         </row>
         <row r="50">
           <cell r="L50">
-            <v>0.225559165944784</v>
+            <v>0.22555916594478401</v>
           </cell>
         </row>
         <row r="51">
@@ -3172,7 +2661,7 @@
         </row>
         <row r="52">
           <cell r="L52">
-            <v>0.201427126315792</v>
+            <v>0.20142712631579199</v>
           </cell>
         </row>
         <row r="53">
@@ -3187,12 +2676,12 @@
         </row>
         <row r="55">
           <cell r="L55">
-            <v>0.175197070022782</v>
+            <v>0.17519707002278201</v>
           </cell>
         </row>
         <row r="56">
           <cell r="L56">
-            <v>0.162105908361236</v>
+            <v>0.16210590836123601</v>
           </cell>
         </row>
         <row r="57">
@@ -3202,12 +2691,12 @@
         </row>
         <row r="58">
           <cell r="L58">
-            <v>0.155058469203377</v>
+            <v>0.15505846920337699</v>
           </cell>
         </row>
         <row r="59">
           <cell r="L59">
-            <v>0.153476033552131</v>
+            <v>0.15347603355213099</v>
           </cell>
         </row>
         <row r="60">
@@ -3217,17 +2706,17 @@
         </row>
         <row r="61">
           <cell r="L61">
-            <v>0.151350526540712</v>
+            <v>0.15135052654071199</v>
           </cell>
         </row>
         <row r="62">
           <cell r="L62">
-            <v>0.145204482579299</v>
+            <v>0.14520448257929899</v>
           </cell>
         </row>
         <row r="63">
           <cell r="L63">
-            <v>0.140294528147456</v>
+            <v>0.14029452814745599</v>
           </cell>
         </row>
         <row r="64">
@@ -3237,7 +2726,7 @@
         </row>
         <row r="65">
           <cell r="L65">
-            <v>0.137650677988234</v>
+            <v>0.13765067798823399</v>
           </cell>
         </row>
       </sheetData>
@@ -3499,135 +2988,136 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="14" t="s">
+      <c r="B1" s="12"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>2021</v>
       </c>
     </row>
-    <row r="8" spans="2:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="2:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="2:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>2020</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="15" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="14" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1" display="http://www.stats.gov.cn/tjsj/ndsj/2021/indexch.htm" tooltip="http://www.stats.gov.cn/tjsj/ndsj/2021/indexch.htm"/>
-    <hyperlink ref="B13" r:id="rId1" display="http://www.stats.gov.cn/tjsj/ndsj/2021/indexch.htm" tooltip="http://www.stats.gov.cn/tjsj/ndsj/2021/indexch.htm"/>
-    <hyperlink ref="B18" r:id="rId2" display="https://data.stats.gov.cn/easyquery.htm?cn=C01"/>
+    <hyperlink ref="B8" r:id="rId1" tooltip="http://www.stats.gov.cn/tjsj/ndsj/2021/indexch.htm" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B13" r:id="rId2" tooltip="http://www.stats.gov.cn/tjsj/ndsj/2021/indexch.htm" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B18" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:S74"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:S75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.25" customWidth="1"/>
-    <col min="2" max="19" width="9.625" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="2" max="6" width="9.6640625" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" customWidth="1"/>
+    <col min="8" max="19" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>15</v>
       </c>
@@ -3683,7 +3173,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -3691,40 +3181,40 @@
         <v>36914557</v>
       </c>
       <c r="C2">
-        <v>28791080.8702537</v>
+        <v>28791080.870253701</v>
       </c>
       <c r="D2">
-        <v>24265336.046334</v>
+        <v>24265336.046333998</v>
       </c>
       <c r="E2">
-        <v>23277788.3921946</v>
+        <v>23277788.392194599</v>
       </c>
       <c r="F2">
-        <v>23723586.3691048</v>
+        <v>23723586.369104799</v>
       </c>
       <c r="G2">
-        <v>25210372.2468704</v>
+        <v>25210372.246870399</v>
       </c>
       <c r="H2">
         <v>25263955.0396505</v>
       </c>
       <c r="I2">
-        <v>22830053.9735202</v>
+        <v>22830053.973520201</v>
       </c>
       <c r="J2">
-        <v>19518675.5743014</v>
+        <v>19518675.574301399</v>
       </c>
       <c r="K2">
         <v>40969331</v>
       </c>
       <c r="L2">
-        <v>30230634.9137663</v>
+        <v>30230634.913766298</v>
       </c>
       <c r="M2">
-        <v>25478602.8486507</v>
+        <v>25478602.848650701</v>
       </c>
       <c r="N2">
-        <v>24441677.8118044</v>
+        <v>24441677.811804399</v>
       </c>
       <c r="O2">
         <v>24909765.68756</v>
@@ -3733,16 +3223,16 @@
         <v>26470890.8592139</v>
       </c>
       <c r="Q2">
-        <v>26527152.791633</v>
+        <v>26527152.791632999</v>
       </c>
       <c r="R2">
-        <v>23971556.6721962</v>
+        <v>23971556.672196198</v>
       </c>
       <c r="S2">
-        <v>20494609.3530164</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
+        <v>20494609.353016399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -3750,58 +3240,58 @@
         <v>42226598</v>
       </c>
       <c r="C3">
-        <v>36807504.7847</v>
+        <v>36807504.784699999</v>
       </c>
       <c r="D3">
-        <v>28710465.8438169</v>
+        <v>28710465.843816899</v>
       </c>
       <c r="E3">
-        <v>24197393.1054043</v>
+        <v>24197393.105404299</v>
       </c>
       <c r="F3">
-        <v>23214938.3635357</v>
+        <v>23214938.363535699</v>
       </c>
       <c r="G3">
-        <v>23659532.6859082</v>
+        <v>23659532.685908198</v>
       </c>
       <c r="H3">
-        <v>25144825.2790285</v>
+        <v>25144825.279028501</v>
       </c>
       <c r="I3">
-        <v>25198268.7565474</v>
+        <v>25198268.756547399</v>
       </c>
       <c r="J3">
-        <v>22772978.8385864</v>
+        <v>22772978.838586401</v>
       </c>
       <c r="K3">
         <v>48017458</v>
       </c>
       <c r="L3">
-        <v>40825938.3415</v>
+        <v>40825938.341499999</v>
       </c>
       <c r="M3">
-        <v>30127850.7550595</v>
+        <v>30127850.755059499</v>
       </c>
       <c r="N3">
         <v>25394523.4592501</v>
       </c>
       <c r="O3">
-        <v>24361020.2750254</v>
+        <v>24361020.275025401</v>
       </c>
       <c r="P3">
-        <v>24830054.4373598</v>
+        <v>24830054.437359799</v>
       </c>
       <c r="Q3">
-        <v>26388831.0975503</v>
+        <v>26388831.097550299</v>
       </c>
       <c r="R3">
         <v>26447571.3332581</v>
       </c>
       <c r="S3">
-        <v>23899642.0021797</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
+        <v>23899642.002179701</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -3809,58 +3299,58 @@
         <v>39649204</v>
       </c>
       <c r="C4">
-        <v>42197039.3814</v>
+        <v>42197039.381399997</v>
       </c>
       <c r="D4">
-        <v>36781739.5313507</v>
+        <v>36781739.531350702</v>
       </c>
       <c r="E4">
         <v>28693239.5643107</v>
       </c>
       <c r="F4">
-        <v>24182874.669541</v>
+        <v>24182874.669541001</v>
       </c>
       <c r="G4">
         <v>23203330.8943539</v>
       </c>
       <c r="H4">
-        <v>23647702.9195653</v>
+        <v>23647702.919565301</v>
       </c>
       <c r="I4">
-        <v>25132252.866389</v>
+        <v>25132252.866388999</v>
       </c>
       <c r="J4">
-        <v>25188189.4490448</v>
+        <v>25188189.449044801</v>
       </c>
       <c r="K4">
         <v>45606790</v>
       </c>
       <c r="L4">
-        <v>47969440.542</v>
+        <v>47969440.542000003</v>
       </c>
       <c r="M4">
-        <v>40789194.9969926</v>
+        <v>40789194.996992603</v>
       </c>
       <c r="N4">
-        <v>30103748.4744555</v>
+        <v>30103748.474455498</v>
       </c>
       <c r="O4">
-        <v>25374207.8404827</v>
+        <v>25374207.840482701</v>
       </c>
       <c r="P4">
-        <v>24343967.5608329</v>
+        <v>24343967.560832899</v>
       </c>
       <c r="Q4">
         <v>24815156.4046974</v>
       </c>
       <c r="R4">
-        <v>26372997.7988918</v>
+        <v>26372997.798891801</v>
       </c>
       <c r="S4">
         <v>26434347.5475915</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -3868,28 +3358,28 @@
         <v>33630797</v>
       </c>
       <c r="C5">
-        <v>39609554.796</v>
+        <v>39609554.795999996</v>
       </c>
       <c r="D5">
-        <v>42159062.0459567</v>
+        <v>42159062.045956701</v>
       </c>
       <c r="E5">
-        <v>36752314.1397256</v>
+        <v>36752314.139725603</v>
       </c>
       <c r="F5">
-        <v>28673154.2966156</v>
+        <v>28673154.296615601</v>
       </c>
       <c r="G5">
-        <v>24168364.9447393</v>
+        <v>24168364.944739301</v>
       </c>
       <c r="H5">
-        <v>23189408.8958173</v>
+        <v>23189408.895817298</v>
       </c>
       <c r="I5">
         <v>23635879.0681055</v>
       </c>
       <c r="J5">
-        <v>25122199.9652424</v>
+        <v>25122199.965242401</v>
       </c>
       <c r="K5">
         <v>39053343</v>
@@ -3898,28 +3388,28 @@
         <v>45547501.173</v>
       </c>
       <c r="M5">
-        <v>47911877.2133496</v>
+        <v>47911877.213349603</v>
       </c>
       <c r="N5">
-        <v>40748405.8019957</v>
+        <v>40748405.801995702</v>
       </c>
       <c r="O5">
-        <v>30076655.1008285</v>
+        <v>30076655.100828499</v>
       </c>
       <c r="P5">
         <v>25353908.4742104</v>
       </c>
       <c r="Q5">
-        <v>24326926.7835403</v>
+        <v>24326926.783540301</v>
       </c>
       <c r="R5">
-        <v>24800267.3108546</v>
+        <v>24800267.310854599</v>
       </c>
       <c r="S5">
-        <v>26357174.0002125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
+        <v>26357174.000212502</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -3930,55 +3420,55 @@
         <v>33590440.0436</v>
       </c>
       <c r="D6">
-        <v>39565984.2857244</v>
+        <v>39565984.285724401</v>
       </c>
       <c r="E6">
-        <v>42116902.9839108</v>
+        <v>42116902.983910799</v>
       </c>
       <c r="F6">
-        <v>36715561.8255859</v>
+        <v>36715561.825585902</v>
       </c>
       <c r="G6">
         <v>28647348.4577487</v>
       </c>
       <c r="H6">
-        <v>24146613.416289</v>
+        <v>24146613.416289002</v>
       </c>
       <c r="I6">
-        <v>23170857.3687007</v>
+        <v>23170857.368700702</v>
       </c>
       <c r="J6">
-        <v>23619333.9527578</v>
+        <v>23619333.952757802</v>
       </c>
       <c r="K6">
         <v>39675995</v>
       </c>
       <c r="L6">
-        <v>38963520.3111</v>
+        <v>38963520.311099999</v>
       </c>
       <c r="M6">
-        <v>45447296.6704194</v>
+        <v>45447296.670419402</v>
       </c>
       <c r="N6">
         <v>47816053.4589229</v>
       </c>
       <c r="O6">
-        <v>40670983.8309719</v>
+        <v>40670983.830971897</v>
       </c>
       <c r="P6">
         <v>30022517.121647</v>
       </c>
       <c r="Q6">
-        <v>25310806.8298042</v>
+        <v>25310806.829804201</v>
       </c>
       <c r="R6">
         <v>24288003.7006866</v>
       </c>
       <c r="S6">
-        <v>24763066.9098883</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19">
+        <v>24763066.909888301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -3986,58 +3476,58 @@
         <v>43685062</v>
       </c>
       <c r="C7">
-        <v>35219834.616</v>
+        <v>35219834.615999997</v>
       </c>
       <c r="D7">
-        <v>33546772.4715433</v>
+        <v>33546772.471543301</v>
       </c>
       <c r="E7">
-        <v>39518505.1045815</v>
+        <v>39518505.104581498</v>
       </c>
       <c r="F7">
-        <v>42066362.7003301</v>
+        <v>42066362.700330101</v>
       </c>
       <c r="G7">
-        <v>36675174.7075778</v>
+        <v>36675174.707577802</v>
       </c>
       <c r="H7">
         <v>28615836.3744452</v>
       </c>
       <c r="I7">
-        <v>24120052.1415311</v>
+        <v>24120052.141531099</v>
       </c>
       <c r="J7">
-        <v>23147686.511332</v>
+        <v>23147686.511332002</v>
       </c>
       <c r="K7">
         <v>48162270</v>
       </c>
       <c r="L7">
-        <v>39568869.8135</v>
+        <v>39568869.813500002</v>
       </c>
       <c r="M7">
-        <v>38858318.80626</v>
+        <v>38858318.806259997</v>
       </c>
       <c r="N7">
-        <v>45329133.6990763</v>
+        <v>45329133.699076302</v>
       </c>
       <c r="O7">
-        <v>47691731.7199297</v>
+        <v>47691731.719929703</v>
       </c>
       <c r="P7">
-        <v>40565239.2730113</v>
+        <v>40565239.273011297</v>
       </c>
       <c r="Q7">
-        <v>29944458.5771307</v>
+        <v>29944458.577130701</v>
       </c>
       <c r="R7">
-        <v>25247529.8127297</v>
+        <v>25247529.812729701</v>
       </c>
       <c r="S7">
-        <v>24227283.6914349</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
+        <v>24227283.691434901</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -4045,58 +3535,58 @@
         <v>60273382</v>
       </c>
       <c r="C8">
-        <v>43623902.9132</v>
+        <v>43623902.913199998</v>
       </c>
       <c r="D8">
         <v>35170526.8475376</v>
       </c>
       <c r="E8">
-        <v>33499806.9900832</v>
+        <v>33499806.990083199</v>
       </c>
       <c r="F8">
-        <v>39463179.1974351</v>
+        <v>39463179.197435103</v>
       </c>
       <c r="G8">
-        <v>42011676.4288197</v>
+        <v>42011676.428819701</v>
       </c>
       <c r="H8">
-        <v>36627496.9804579</v>
+        <v>36627496.980457902</v>
       </c>
       <c r="I8">
         <v>28578635.7871584</v>
       </c>
       <c r="J8">
-        <v>24088696.0737471</v>
+        <v>24088696.073747098</v>
       </c>
       <c r="K8">
         <v>63871808</v>
       </c>
       <c r="L8">
-        <v>48003334.509</v>
+        <v>48003334.509000003</v>
       </c>
       <c r="M8">
-        <v>39442249.4300968</v>
+        <v>39442249.430096798</v>
       </c>
       <c r="N8">
-        <v>38733972.18608</v>
+        <v>38733972.186080001</v>
       </c>
       <c r="O8">
         <v>45188613.3846092</v>
       </c>
       <c r="P8">
-        <v>47548656.5247699</v>
+        <v>47548656.524769902</v>
       </c>
       <c r="Q8">
-        <v>40443543.5551923</v>
+        <v>40443543.555192299</v>
       </c>
       <c r="R8">
         <v>29857619.647257</v>
       </c>
       <c r="S8">
-        <v>25174311.9762728</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
+        <v>25174311.976272799</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -4104,58 +3594,58 @@
         <v>48080895</v>
       </c>
       <c r="C9">
-        <v>60158862.5742</v>
+        <v>60158862.574199997</v>
       </c>
       <c r="D9">
-        <v>43541017.4976649</v>
+        <v>43541017.497664899</v>
       </c>
       <c r="E9">
-        <v>35107219.899212</v>
+        <v>35107219.899212003</v>
       </c>
       <c r="F9">
-        <v>33439507.337501</v>
+        <v>33439507.337501001</v>
       </c>
       <c r="G9">
-        <v>39392145.4748797</v>
+        <v>39392145.474879697</v>
       </c>
       <c r="H9">
-        <v>41936055.4112478</v>
+        <v>41936055.411247797</v>
       </c>
       <c r="I9">
-        <v>36565230.2355911</v>
+        <v>36565230.235591099</v>
       </c>
       <c r="J9">
-        <v>28530052.1063202</v>
+        <v>28530052.106320199</v>
       </c>
       <c r="K9">
         <v>50932037</v>
       </c>
       <c r="L9">
-        <v>63590772.0448</v>
+        <v>63590772.044799998</v>
       </c>
       <c r="M9">
-        <v>47801720.5040622</v>
+        <v>47801720.504062198</v>
       </c>
       <c r="N9">
-        <v>39280536.2074334</v>
+        <v>39280536.207433403</v>
       </c>
       <c r="O9">
-        <v>38582909.6945543</v>
+        <v>38582909.694554299</v>
       </c>
       <c r="P9">
         <v>45016896.6537477</v>
       </c>
       <c r="Q9">
-        <v>47377481.3612807</v>
+        <v>47377481.361280702</v>
       </c>
       <c r="R9">
-        <v>40301991.1527491</v>
+        <v>40301991.152749099</v>
       </c>
       <c r="S9">
         <v>29759089.5024211</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -4163,58 +3653,58 @@
         <v>45322636</v>
       </c>
       <c r="C10">
-        <v>47951076.5835</v>
+        <v>47951076.583499998</v>
       </c>
       <c r="D10">
-        <v>59996433.6452497</v>
+        <v>59996433.645249702</v>
       </c>
       <c r="E10">
-        <v>43427810.852171</v>
+        <v>43427810.852170996</v>
       </c>
       <c r="F10">
-        <v>35015941.1274741</v>
+        <v>35015941.127474099</v>
       </c>
       <c r="G10">
-        <v>33355908.5691573</v>
+        <v>33355908.569157299</v>
       </c>
       <c r="H10">
-        <v>39293665.1111925</v>
+        <v>39293665.111192502</v>
       </c>
       <c r="I10">
-        <v>41831215.2727197</v>
+        <v>41831215.272719704</v>
       </c>
       <c r="J10">
-        <v>36477473.6830257</v>
+        <v>36477473.683025703</v>
       </c>
       <c r="K10">
         <v>47632694</v>
       </c>
       <c r="L10">
-        <v>50580605.9447</v>
+        <v>50580605.944700003</v>
       </c>
       <c r="M10">
-        <v>63177432.0265088</v>
+        <v>63177432.026508801</v>
       </c>
       <c r="N10">
-        <v>47510130.0089874</v>
+        <v>47510130.008987397</v>
       </c>
       <c r="O10">
         <v>39056637.151051</v>
       </c>
       <c r="P10">
-        <v>38378420.2731731</v>
+        <v>38378420.273173101</v>
       </c>
       <c r="Q10">
-        <v>44791812.1704789</v>
+        <v>44791812.170478903</v>
       </c>
       <c r="R10">
-        <v>47154807.1988827</v>
+        <v>47154807.198882699</v>
       </c>
       <c r="S10">
         <v>40124662.391677</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -4222,58 +3712,58 @@
         <v>56033201</v>
       </c>
       <c r="C11">
-        <v>45127748.6652</v>
+        <v>45127748.665200002</v>
       </c>
       <c r="D11">
-        <v>47749682.0618493</v>
+        <v>47749682.061849304</v>
       </c>
       <c r="E11">
         <v>59750448.2673041</v>
       </c>
       <c r="F11">
-        <v>43249756.8276771</v>
+        <v>43249756.827677101</v>
       </c>
       <c r="G11">
-        <v>34875877.3629642</v>
+        <v>34875877.362964198</v>
       </c>
       <c r="H11">
-        <v>33225820.5257376</v>
+        <v>33225820.525737599</v>
       </c>
       <c r="I11">
-        <v>39144349.18377</v>
+        <v>39144349.183770001</v>
       </c>
       <c r="J11">
-        <v>41672256.6546833</v>
+        <v>41672256.654683299</v>
       </c>
       <c r="K11">
         <v>58191686</v>
       </c>
       <c r="L11">
-        <v>47108734.366</v>
+        <v>47108734.365999997</v>
       </c>
       <c r="M11">
-        <v>50059625.7034696</v>
+        <v>50059625.703469597</v>
       </c>
       <c r="N11">
-        <v>62570928.6790543</v>
+        <v>62570928.679054298</v>
       </c>
       <c r="O11">
-        <v>47087289.8519074</v>
+        <v>47087289.851907402</v>
       </c>
       <c r="P11">
-        <v>38732467.0626973</v>
+        <v>38732467.062697299</v>
       </c>
       <c r="Q11">
         <v>38079068.5950424</v>
       </c>
       <c r="R11">
-        <v>44469311.1228515</v>
+        <v>44469311.122851498</v>
       </c>
       <c r="S11">
-        <v>46834154.5099303</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19">
+        <v>46834154.509930298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -4281,28 +3771,28 @@
         <v>60058826</v>
       </c>
       <c r="C12">
-        <v>55640968.593</v>
+        <v>55640968.593000002</v>
       </c>
       <c r="D12">
-        <v>44820879.9742766</v>
+        <v>44820879.974276602</v>
       </c>
       <c r="E12">
-        <v>47434534.1602411</v>
+        <v>47434534.160241097</v>
       </c>
       <c r="F12">
-        <v>59362070.3535667</v>
+        <v>59362070.353566699</v>
       </c>
       <c r="G12">
-        <v>42977283.3596627</v>
+        <v>42977283.359662697</v>
       </c>
       <c r="H12">
-        <v>34659646.9233138</v>
+        <v>34659646.923313797</v>
       </c>
       <c r="I12">
-        <v>33026465.6025831</v>
+        <v>33026465.602583099</v>
       </c>
       <c r="J12">
-        <v>38917311.9585041</v>
+        <v>38917311.958504103</v>
       </c>
       <c r="K12">
         <v>61105470</v>
@@ -4311,28 +3801,28 @@
         <v>57214065.6752</v>
       </c>
       <c r="M12">
-        <v>46369127.2364538</v>
+        <v>46369127.236453801</v>
       </c>
       <c r="N12">
-        <v>49323749.2056286</v>
+        <v>49323749.205628604</v>
       </c>
       <c r="O12">
-        <v>61707449.8632834</v>
+        <v>61707449.863283403</v>
       </c>
       <c r="P12">
-        <v>46479863.8128178</v>
+        <v>46479863.812817797</v>
       </c>
       <c r="Q12">
-        <v>38263804.2112387</v>
+        <v>38263804.211238697</v>
       </c>
       <c r="R12">
-        <v>37648775.1199184</v>
+        <v>37648775.119918399</v>
       </c>
       <c r="S12">
-        <v>43997936.4249492</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19">
+        <v>43997936.424949199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -4340,40 +3830,40 @@
         <v>50584760</v>
       </c>
       <c r="C13">
-        <v>59368149.501</v>
+        <v>59368149.501000002</v>
       </c>
       <c r="D13">
-        <v>55023353.8416177</v>
+        <v>55023353.841617703</v>
       </c>
       <c r="E13">
         <v>44341296.5585519</v>
       </c>
       <c r="F13">
-        <v>46941215.0049746</v>
+        <v>46941215.004974604</v>
       </c>
       <c r="G13">
         <v>58768449.650031</v>
       </c>
       <c r="H13">
-        <v>42560403.711074</v>
+        <v>42560403.711074002</v>
       </c>
       <c r="I13">
-        <v>34337312.206927</v>
+        <v>34337312.206927001</v>
       </c>
       <c r="J13">
-        <v>32729227.4121599</v>
+        <v>32729227.412159901</v>
       </c>
       <c r="K13">
         <v>50816026</v>
       </c>
       <c r="L13">
-        <v>59528948.874</v>
+        <v>59528948.873999998</v>
       </c>
       <c r="M13">
         <v>55823763.8792926</v>
       </c>
       <c r="N13">
-        <v>45307274.222739</v>
+        <v>45307274.222739004</v>
       </c>
       <c r="O13">
         <v>48258356.222787</v>
@@ -4382,16 +3872,16 @@
         <v>60454788.6310587</v>
       </c>
       <c r="Q13">
-        <v>45592098.413993</v>
+        <v>45592098.413993001</v>
       </c>
       <c r="R13">
-        <v>37575055.7354364</v>
+        <v>37575055.735436402</v>
       </c>
       <c r="S13">
-        <v>37008745.9428798</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19">
+        <v>37008745.942879803</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -4399,25 +3889,25 @@
         <v>36511813</v>
       </c>
       <c r="C14">
-        <v>49694468.224</v>
+        <v>49694468.223999999</v>
       </c>
       <c r="D14">
         <v>58370764.5893832</v>
       </c>
       <c r="E14">
-        <v>54137477.8447677</v>
+        <v>54137477.844767697</v>
       </c>
       <c r="F14">
-        <v>43662874.721206</v>
+        <v>43662874.721206002</v>
       </c>
       <c r="G14">
-        <v>46251179.1444015</v>
+        <v>46251179.144401498</v>
       </c>
       <c r="H14">
-        <v>57945691.3549306</v>
+        <v>57945691.354930602</v>
       </c>
       <c r="I14">
-        <v>41990094.3013456</v>
+        <v>41990094.301345602</v>
       </c>
       <c r="J14">
         <v>33897794.6106783</v>
@@ -4426,31 +3916,31 @@
         <v>36871125</v>
       </c>
       <c r="L14">
-        <v>48768140.1522</v>
+        <v>48768140.152199998</v>
       </c>
       <c r="M14">
         <v>57260895.9219006</v>
       </c>
       <c r="N14">
-        <v>53814108.3796381</v>
+        <v>53814108.379638098</v>
       </c>
       <c r="O14">
-        <v>43766826.8991659</v>
+        <v>43766826.899165899</v>
       </c>
       <c r="P14">
-        <v>46704437.1524133</v>
+        <v>46704437.152413301</v>
       </c>
       <c r="Q14">
-        <v>58616963.0566745</v>
+        <v>58616963.056674503</v>
       </c>
       <c r="R14">
-        <v>44279045.97967</v>
+        <v>44279045.979670003</v>
       </c>
       <c r="S14">
-        <v>36553014.2194325</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19">
+        <v>36553014.219432503</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -4458,28 +3948,28 @@
         <v>37667637</v>
       </c>
       <c r="C15">
-        <v>35463923.9669</v>
+        <v>35463923.966899998</v>
       </c>
       <c r="D15">
-        <v>48342778.6883072</v>
+        <v>48342778.688307203</v>
       </c>
       <c r="E15">
         <v>56870635.9394361</v>
       </c>
       <c r="F15">
-        <v>52821937.1331398</v>
+        <v>52821937.133139797</v>
       </c>
       <c r="G15">
-        <v>42658628.6026183</v>
+        <v>42658628.602618299</v>
       </c>
       <c r="H15">
-        <v>45242903.4390535</v>
+        <v>45242903.439053498</v>
       </c>
       <c r="I15">
-        <v>56752010.113019</v>
+        <v>56752010.113018997</v>
       </c>
       <c r="J15">
-        <v>41171287.4624694</v>
+        <v>41171287.462469399</v>
       </c>
       <c r="K15">
         <v>36337923</v>
@@ -4488,28 +3978,28 @@
         <v>34585115.25</v>
       </c>
       <c r="M15">
-        <v>45885943.069205</v>
+        <v>45885943.069205001</v>
       </c>
       <c r="N15">
-        <v>54031381.3919054</v>
+        <v>54031381.391905397</v>
       </c>
       <c r="O15">
-        <v>50918909.3488136</v>
+        <v>50918909.348813601</v>
       </c>
       <c r="P15">
-        <v>41521588.6792387</v>
+        <v>41521588.679238699</v>
       </c>
       <c r="Q15">
-        <v>44415919.731945</v>
+        <v>44415919.731945001</v>
       </c>
       <c r="R15">
-        <v>55879550.8819278</v>
+        <v>55879550.881927803</v>
       </c>
       <c r="S15">
-        <v>42304200.5289767</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19">
+        <v>42304200.528976701</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -4517,49 +4007,49 @@
         <v>25427303</v>
       </c>
       <c r="C16">
-        <v>35780488.3863</v>
+        <v>35780488.386299998</v>
       </c>
       <c r="D16">
-        <v>33821944.2872325</v>
+        <v>33821944.287232503</v>
       </c>
       <c r="E16">
-        <v>46278542.0383165</v>
+        <v>46278542.038316503</v>
       </c>
       <c r="F16">
-        <v>54624245.8198283</v>
+        <v>54624245.819828302</v>
       </c>
       <c r="G16">
-        <v>50899218.6214935</v>
+        <v>50899218.621493503</v>
       </c>
       <c r="H16">
-        <v>41225298.6815703</v>
+        <v>41225298.681570299</v>
       </c>
       <c r="I16">
-        <v>43835849.1420989</v>
+        <v>43835849.142098904</v>
       </c>
       <c r="J16">
-        <v>55123227.4227754</v>
+        <v>55123227.422775403</v>
       </c>
       <c r="K16">
         <v>24162733</v>
       </c>
       <c r="L16">
-        <v>32871285.1458</v>
+        <v>32871285.145799998</v>
       </c>
       <c r="M16">
-        <v>31448245.296825</v>
+        <v>31448245.296824999</v>
       </c>
       <c r="N16">
-        <v>41930574.7766395</v>
+        <v>41930574.776639499</v>
       </c>
       <c r="O16">
-        <v>49600808.1177692</v>
+        <v>49600808.117769197</v>
       </c>
       <c r="P16">
-        <v>46947234.4196061</v>
+        <v>46947234.419606097</v>
       </c>
       <c r="Q16">
-        <v>38444838.9581071</v>
+        <v>38444838.958107099</v>
       </c>
       <c r="R16">
         <v>41284597.3908429</v>
@@ -4568,7 +4058,7 @@
         <v>52135620.9728387</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -4576,7 +4066,7 @@
         <v>16486416</v>
       </c>
       <c r="C17">
-        <v>23077820.2028</v>
+        <v>23077820.202799998</v>
       </c>
       <c r="D17">
         <v>32764193.2153349</v>
@@ -4585,49 +4075,49 @@
         <v>31221036.7715443</v>
       </c>
       <c r="F17">
-        <v>43034416.2414305</v>
+        <v>43034416.241430499</v>
       </c>
       <c r="G17">
-        <v>51128294.0873593</v>
+        <v>51128294.087359302</v>
       </c>
       <c r="H17">
-        <v>47926704.2539983</v>
+        <v>47926704.253998302</v>
       </c>
       <c r="I17">
-        <v>39032112.7917108</v>
+        <v>39032112.791710801</v>
       </c>
       <c r="J17">
-        <v>41705426.8737929</v>
+        <v>41705426.873792902</v>
       </c>
       <c r="K17">
         <v>14752433</v>
       </c>
       <c r="L17">
-        <v>20429590.7515</v>
+        <v>20429590.751499999</v>
       </c>
       <c r="M17">
-        <v>28049067.6149111</v>
+        <v>28049067.614911102</v>
       </c>
       <c r="N17">
         <v>27067504.7269773</v>
       </c>
       <c r="O17">
-        <v>36383159.7336901</v>
+        <v>36383159.733690098</v>
       </c>
       <c r="P17">
-        <v>43370946.6181774</v>
+        <v>43370946.618177399</v>
       </c>
       <c r="Q17">
         <v>41346429.3533471</v>
       </c>
       <c r="R17">
-        <v>34092883.1880494</v>
+        <v>34092883.188049398</v>
       </c>
       <c r="S17">
         <v>36846503.1713273</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -4638,55 +4128,55 @@
         <v>13715049.4704</v>
       </c>
       <c r="D18">
-        <v>19556144.8398527</v>
+        <v>19556144.839852698</v>
       </c>
       <c r="E18">
-        <v>28223076.0356895</v>
+        <v>28223076.035689499</v>
       </c>
       <c r="F18">
-        <v>27290308.2420069</v>
+        <v>27290308.242006902</v>
       </c>
       <c r="G18">
-        <v>38115582.465035</v>
+        <v>38115582.465034999</v>
       </c>
       <c r="H18">
-        <v>45821177.1610914</v>
+        <v>45821177.161091402</v>
       </c>
       <c r="I18">
         <v>43412008.7132717</v>
       </c>
       <c r="J18">
-        <v>35690963.9367403</v>
+        <v>35690963.936740302</v>
       </c>
       <c r="K18">
         <v>9157003</v>
       </c>
       <c r="L18">
-        <v>11083502.9129</v>
+        <v>11083502.912900001</v>
       </c>
       <c r="M18">
-        <v>15616379.1704466</v>
+        <v>15616379.170446601</v>
       </c>
       <c r="N18">
-        <v>21788515.723263</v>
+        <v>21788515.723262999</v>
       </c>
       <c r="O18">
-        <v>21345434.2276943</v>
+        <v>21345434.227694299</v>
       </c>
       <c r="P18">
-        <v>29099251.1550053</v>
+        <v>29099251.155005299</v>
       </c>
       <c r="Q18">
-        <v>35143478.0447091</v>
+        <v>35143478.044709101</v>
       </c>
       <c r="R18">
-        <v>33916475.9985506</v>
+        <v>33916475.998550601</v>
       </c>
       <c r="S18">
-        <v>28290274.4694434</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19">
+        <v>28290274.469443399</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -4694,7 +4184,7 @@
         <v>6400439</v>
       </c>
       <c r="C19">
-        <v>7876073.9</v>
+        <v>7876073.9000000004</v>
       </c>
       <c r="D19">
         <v>9961240.43035152</v>
@@ -4706,28 +4196,28 @@
         <v>21723301.6246702</v>
       </c>
       <c r="G19">
-        <v>21526595.1412951</v>
+        <v>21526595.141295101</v>
       </c>
       <c r="H19">
-        <v>30732594.1415577</v>
+        <v>30732594.141557701</v>
       </c>
       <c r="I19">
-        <v>37678753.9795655</v>
+        <v>37678753.979565501</v>
       </c>
       <c r="J19">
-        <v>36335851.2930084</v>
+        <v>36335851.293008402</v>
       </c>
       <c r="K19">
         <v>4426091</v>
       </c>
       <c r="L19">
-        <v>5560132.2216</v>
+        <v>5560132.2215999998</v>
       </c>
       <c r="M19">
-        <v>6913889.11706702</v>
+        <v>6913889.1170670204</v>
       </c>
       <c r="N19">
-        <v>9989797.75533469</v>
+        <v>9989797.7553346902</v>
       </c>
       <c r="O19">
         <v>14271477.7987372</v>
@@ -4736,16 +4226,16 @@
         <v>14290768.2154413</v>
       </c>
       <c r="Q19">
-        <v>19889338.1644461</v>
+        <v>19889338.164446101</v>
       </c>
       <c r="R19">
-        <v>24491489.8493578</v>
+        <v>24491489.849357799</v>
       </c>
       <c r="S19">
         <v>24070523.0161714</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -4753,16 +4243,16 @@
         <v>2285155</v>
       </c>
       <c r="C20">
-        <v>3358310.3433</v>
+        <v>3358310.3432999998</v>
       </c>
       <c r="D20">
-        <v>4364132.54799</v>
+        <v>4364132.5479899999</v>
       </c>
       <c r="E20">
-        <v>5793457.43429244</v>
+        <v>5793457.4342924403</v>
       </c>
       <c r="F20">
-        <v>8896923.37941918</v>
+        <v>8896923.3794191796</v>
       </c>
       <c r="G20">
         <v>13722609.6363042</v>
@@ -4771,40 +4261,40 @@
         <v>14087003.8604635</v>
       </c>
       <c r="I20">
-        <v>20769087.1208647</v>
+        <v>20769087.120864701</v>
       </c>
       <c r="J20">
-        <v>26216877.0189817</v>
+        <v>26216877.018981699</v>
       </c>
       <c r="K20">
         <v>1367594</v>
       </c>
       <c r="L20">
-        <v>1951463.5219</v>
+        <v>1951463.5219000001</v>
       </c>
       <c r="M20">
         <v>2532640.2269388</v>
       </c>
       <c r="N20">
-        <v>3248145.10719809</v>
+        <v>3248145.1071980898</v>
       </c>
       <c r="O20">
-        <v>4832065.17425539</v>
+        <v>4832065.1742553897</v>
       </c>
       <c r="P20">
-        <v>7095778.76153216</v>
+        <v>7095778.7615321605</v>
       </c>
       <c r="Q20">
-        <v>7292579.02033971</v>
+        <v>7292579.0203397097</v>
       </c>
       <c r="R20">
         <v>10406101.7276382</v>
       </c>
       <c r="S20">
-        <v>13117641.963316</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19">
+        <v>13117641.963315999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -4821,49 +4311,49 @@
         <v>1622148.06808788</v>
       </c>
       <c r="F21">
-        <v>2288995.03228894</v>
+        <v>2288995.0322889402</v>
       </c>
       <c r="G21">
-        <v>3716244.89558339</v>
+        <v>3716244.8955833898</v>
       </c>
       <c r="H21">
-        <v>6029714.67419205</v>
+        <v>6029714.6741920495</v>
       </c>
       <c r="I21">
         <v>6485656.57735739</v>
       </c>
       <c r="J21">
-        <v>9979546.36157549</v>
+        <v>9979546.3615754899</v>
       </c>
       <c r="K21">
         <v>271455</v>
       </c>
       <c r="L21">
-        <v>385387.9892</v>
+        <v>385387.98920000001</v>
       </c>
       <c r="M21">
-        <v>565534.12864662</v>
+        <v>565534.12864661997</v>
       </c>
       <c r="N21">
-        <v>753966.995559681</v>
+        <v>753966.99555968097</v>
       </c>
       <c r="O21">
-        <v>992633.144759735</v>
+        <v>992633.14475973498</v>
       </c>
       <c r="P21">
-        <v>1513886.01909421</v>
+        <v>1513886.0190942099</v>
       </c>
       <c r="Q21">
-        <v>2277744.98245182</v>
+        <v>2277744.9824518198</v>
       </c>
       <c r="R21">
         <v>2396341.46608363</v>
       </c>
       <c r="S21">
-        <v>3497490.79065921</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19">
+        <v>3497490.7906592102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -4877,52 +4367,52 @@
         <v>163057.692056</v>
       </c>
       <c r="E22">
-        <v>264409.546011108</v>
+        <v>264409.54601110797</v>
       </c>
       <c r="F22">
-        <v>376013.922182771</v>
+        <v>376013.92218277103</v>
       </c>
       <c r="G22">
-        <v>542034.023646022</v>
+        <v>542034.02364602196</v>
       </c>
       <c r="H22">
-        <v>898588.015752064</v>
+        <v>898588.01575206395</v>
       </c>
       <c r="I22">
-        <v>1488133.5815906</v>
+        <v>1488133.5815906001</v>
       </c>
       <c r="J22">
-        <v>1632439.76052085</v>
+        <v>1632439.7605208501</v>
       </c>
       <c r="K22">
         <v>35129</v>
       </c>
       <c r="L22">
-        <v>61484.5575</v>
+        <v>61484.557500000003</v>
       </c>
       <c r="M22">
-        <v>83860.42644992</v>
+        <v>83860.426449920007</v>
       </c>
       <c r="N22">
         <v>117970.419235685</v>
       </c>
       <c r="O22">
-        <v>150341.0189146</v>
+        <v>150341.01891459999</v>
       </c>
       <c r="P22">
         <v>188798.824133302</v>
       </c>
       <c r="Q22">
-        <v>273861.980854143</v>
+        <v>273861.98085414298</v>
       </c>
       <c r="R22">
-        <v>390405.489992242</v>
+        <v>390405.48999224202</v>
       </c>
       <c r="S22">
-        <v>387967.683358939</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18">
+        <v>387967.68335893902</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>20</v>
       </c>
@@ -4972,7 +4462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -4986,55 +4476,55 @@
       </c>
       <c r="D25">
         <f t="shared" si="0"/>
-        <v>1419485366.60866</v>
+        <v>1419485366.608664</v>
       </c>
       <c r="E25">
         <f t="shared" si="0"/>
-        <v>1406477694.67206</v>
+        <v>1406477694.6720653</v>
       </c>
       <c r="F25">
         <f t="shared" si="0"/>
-        <v>1385994440.2763</v>
+        <v>1385994440.276305</v>
       </c>
       <c r="G25">
         <f t="shared" si="0"/>
-        <v>1360436211.92963</v>
+        <v>1360436211.9296308</v>
       </c>
       <c r="H25">
         <f t="shared" si="0"/>
-        <v>1327783400.25489</v>
+        <v>1327783400.2548852</v>
       </c>
       <c r="I25">
         <f t="shared" si="0"/>
-        <v>1284286657.36219</v>
+        <v>1284286657.3621924</v>
       </c>
       <c r="J25">
         <f t="shared" si="0"/>
-        <v>1229815757.98823</v>
-      </c>
-      <c r="L25" s="11">
+        <v>1229815757.9882255</v>
+      </c>
+      <c r="L25" s="10">
         <v>0.1537335</v>
       </c>
-      <c r="M25" s="11">
+      <c r="M25" s="10">
         <v>-34.64967</v>
       </c>
-      <c r="N25" s="11">
-        <v>3025.144</v>
-      </c>
-      <c r="O25" s="11">
+      <c r="N25" s="10">
+        <v>3025.1439999999998</v>
+      </c>
+      <c r="O25" s="10">
         <v>-127183.4</v>
       </c>
-      <c r="P25" s="11">
+      <c r="P25" s="10">
         <v>2388758</v>
       </c>
-      <c r="Q25" s="11">
+      <c r="Q25" s="10">
         <v>-10543830</v>
       </c>
-      <c r="R25" s="11">
+      <c r="R25" s="10">
         <v>1299652000</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -5044,1018 +4534,1041 @@
       </c>
       <c r="C26">
         <f t="shared" ref="C26:J26" si="1">SUM(C5:C14)+SUM(L5:L14)</f>
-        <v>968859499.3732</v>
+        <v>968859499.37319994</v>
       </c>
       <c r="D26">
         <f t="shared" si="1"/>
-        <v>952096784.652617</v>
+        <v>952096784.65261674</v>
       </c>
       <c r="E26">
         <f t="shared" si="1"/>
-        <v>906520608.650105</v>
+        <v>906520608.65010464</v>
       </c>
       <c r="F26">
         <f t="shared" si="1"/>
-        <v>850677077.111454</v>
+        <v>850677077.11145449</v>
       </c>
       <c r="G26">
         <f t="shared" si="1"/>
-        <v>806380603.079528</v>
+        <v>806380603.07952845</v>
       </c>
       <c r="H26">
         <f t="shared" si="1"/>
-        <v>754947602.258881</v>
+        <v>754947602.25888133</v>
       </c>
       <c r="I26">
         <f t="shared" si="1"/>
-        <v>682022497.949468</v>
+        <v>682022497.94946814</v>
       </c>
       <c r="J26">
         <f t="shared" si="1"/>
-        <v>643001472.497549</v>
-      </c>
-      <c r="L26" s="11">
-        <v>3.700066</v>
-      </c>
-      <c r="M26" s="11">
-        <v>-870.1371</v>
-      </c>
-      <c r="N26" s="11">
+        <v>643001472.4975493</v>
+      </c>
+      <c r="L26" s="10">
+        <v>3.7000660000000001</v>
+      </c>
+      <c r="M26" s="10">
+        <v>-870.13710000000003</v>
+      </c>
+      <c r="N26" s="10">
         <v>82906.44</v>
       </c>
-      <c r="O26" s="11">
+      <c r="O26" s="10">
         <v>-4081690</v>
       </c>
-      <c r="P26" s="11">
+      <c r="P26" s="10">
         <v>108923700</v>
       </c>
-      <c r="Q26" s="11">
+      <c r="Q26" s="10">
         <v>-1491228000</v>
       </c>
-      <c r="R26" s="11">
+      <c r="R26" s="10">
         <v>9157020000</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="10" t="s">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="9" t="s">
         <v>55</v>
       </c>
       <c r="E28" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>2020</v>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
+        <v>2019</v>
       </c>
       <c r="B29">
         <f>A29-2000</f>
+        <v>19</v>
+      </c>
+      <c r="C29" s="10">
+        <f>$L$25*B29^6+$M$25*B29^5+$N$25*B29^4+$O$25*B29^3+$P$25*B29^2+$Q$25*B29+$R$25</f>
+        <v>1404986233.3333836</v>
+      </c>
+      <c r="D29" s="10">
+        <f>$L$26*B29^6+$M$26*B29^5+$N$26*B29^4+$O$26*B29^3+$P$26*B29^2+$Q$26*B29+$R$26</f>
+        <v>972809418.79524612</v>
+      </c>
+      <c r="E29">
+        <f>D29*$B$75</f>
+        <v>756075416.75402272</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2020</v>
+      </c>
+      <c r="B30">
+        <f>A30-2000</f>
         <v>20</v>
       </c>
-      <c r="C29" s="11">
-        <f>$L$25*B29^6+$M$25*B29^5+$N$25*B29^4+$O$25*B29^3+$P$25*B29^2+$Q$25*B29+$R$25</f>
+      <c r="C30" s="19">
+        <f>$L$25*B30^6+$M$25*B30^5+$N$25*B30^4+$O$25*B30^3+$P$25*B30^2+$Q$25*B30+$R$25</f>
         <v>1409794440</v>
       </c>
-      <c r="D29" s="11">
-        <f>$L$26*B29^6+$M$26*B29^5+$N$26*B29^4+$O$26*B29^3+$P$26*B29^2+$Q$26*B29+$R$26</f>
+      <c r="D30" s="10">
+        <f>$L$26*B30^6+$M$26*B30^5+$N$26*B30^4+$O$26*B30^3+$P$26*B30^2+$Q$26*B30+$R$26</f>
         <v>965815904</v>
       </c>
-      <c r="E29">
-        <f>D29*$B$74</f>
-        <v>750640000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
+      <c r="E30">
+        <f>D30*$B$75</f>
+        <v>750639999.99999964</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>2021</v>
       </c>
-      <c r="B30">
-        <f t="shared" ref="B30:B69" si="2">A30-2000</f>
+      <c r="B31">
+        <f t="shared" ref="B31:B70" si="2">A31-2000</f>
         <v>21</v>
       </c>
-      <c r="C30" s="11">
-        <f t="shared" ref="C30:D69" si="3">$L$25*B30^6+$M$25*B30^5+$N$25*B30^4+$O$25*B30^3+$P$25*B30^2+$Q$25*B30+$R$25</f>
-        <v>1413833784.93008</v>
-      </c>
-      <c r="D30" s="11">
-        <f t="shared" ref="D30:D69" si="4">$L$26*B30^6+$M$26*B30^5+$N$26*B30^4+$O$26*B30^3+$P$26*B30^2+$Q$26*B30+$R$26</f>
-        <v>963392475.656887</v>
-      </c>
-      <c r="E30">
-        <f t="shared" ref="E30:E69" si="5">D30*$B$74</f>
-        <v>748756491.720689</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
+      <c r="C31" s="10">
+        <f t="shared" ref="C31:C70" si="3">$L$25*B31^6+$M$25*B31^5+$N$25*B31^4+$O$25*B31^3+$P$25*B31^2+$Q$25*B31+$R$25</f>
+        <v>1413833784.9300835</v>
+      </c>
+      <c r="D31" s="10">
+        <f t="shared" ref="D31:D70" si="4">$L$26*B31^6+$M$26*B31^5+$N$26*B31^4+$O$26*B31^3+$P$26*B31^2+$Q$26*B31+$R$26</f>
+        <v>963392475.65688705</v>
+      </c>
+      <c r="E31">
+        <f t="shared" ref="E31:E70" si="5">D31*$B$75</f>
+        <v>748756491.72068858</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>2022</v>
       </c>
-      <c r="B31">
+      <c r="B32">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C32" s="10">
         <f t="shared" si="3"/>
-        <v>1417114543.03414</v>
-      </c>
-      <c r="D31" s="11">
+        <v>1417114543.0341439</v>
+      </c>
+      <c r="D32" s="10">
         <f t="shared" si="4"/>
-        <v>963717413.566463</v>
-      </c>
-      <c r="E31">
+        <v>963717413.56646347</v>
+      </c>
+      <c r="E32">
         <f t="shared" si="5"/>
-        <v>749009036.114951</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
+        <v>749009036.11495066</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
         <v>2023</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C33" s="10">
         <f t="shared" si="3"/>
-        <v>1419656700.68877</v>
-      </c>
-      <c r="D32" s="11">
+        <v>1419656700.6887715</v>
+      </c>
+      <c r="D33" s="10">
         <f t="shared" si="4"/>
-        <v>965353873.083374</v>
-      </c>
-      <c r="E32">
+        <v>965353873.08337402</v>
+      </c>
+      <c r="E33">
         <f t="shared" si="5"/>
-        <v>750280905.802214</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
+        <v>750280905.80221331</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
         <v>2024</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C34" s="10">
         <f t="shared" si="3"/>
-        <v>1421488177.57082</v>
-      </c>
-      <c r="D33" s="11">
+        <v>1421488177.570816</v>
+      </c>
+      <c r="D34" s="10">
         <f t="shared" si="4"/>
-        <v>967202745.68602</v>
-      </c>
-      <c r="E33">
+        <v>967202745.6860199</v>
+      </c>
+      <c r="E34">
         <f t="shared" si="5"/>
-        <v>751717864.672639</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
+        <v>751717864.67263806</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>2025</v>
       </c>
-      <c r="B34">
+      <c r="B35">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C35" s="10">
         <f t="shared" si="3"/>
-        <v>1422643159.17969</v>
-      </c>
-      <c r="D34" s="11">
+        <v>1422643159.1796875</v>
+      </c>
+      <c r="D35" s="10">
         <f t="shared" si="4"/>
         <v>968458183.59375</v>
       </c>
-      <c r="E34">
+      <c r="E35">
         <f t="shared" si="5"/>
-        <v>752693601.256759</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
+        <v>752693601.25675893</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>2026</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C36" s="10">
         <f t="shared" si="3"/>
-        <v>1423160540.04778</v>
-      </c>
-      <c r="D35" s="11">
+        <v>1423160540.0477757</v>
+      </c>
+      <c r="D36" s="10">
         <f t="shared" si="4"/>
-        <v>968565788.431618</v>
-      </c>
-      <c r="E35">
+        <v>968565788.43161774</v>
+      </c>
+      <c r="E36">
         <f t="shared" si="5"/>
-        <v>752777232.614622</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
+        <v>752777232.61462176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>2027</v>
       </c>
-      <c r="B36">
+      <c r="B37">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C37" s="10">
         <f t="shared" si="3"/>
-        <v>1423082477.63899</v>
-      </c>
-      <c r="D36" s="11">
+        <v>1423082477.6389916</v>
+      </c>
+      <c r="D37" s="10">
         <f t="shared" si="4"/>
-        <v>967183463.942574</v>
-      </c>
-      <c r="E36">
+        <v>967183463.94257355</v>
+      </c>
+      <c r="E37">
         <f t="shared" si="5"/>
-        <v>751702878.744326</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
+        <v>751702878.7443254</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
         <v>2028</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C38" s="10">
         <f t="shared" si="3"/>
-        <v>1422453056.93542</v>
-      </c>
-      <c r="D37" s="11">
+        <v>1422453056.9354239</v>
+      </c>
+      <c r="D38" s="10">
         <f t="shared" si="4"/>
-        <v>964144932.747261</v>
-      </c>
-      <c r="E37">
+        <v>964144932.74726105</v>
+      </c>
+      <c r="E38">
         <f t="shared" si="5"/>
-        <v>749341307.510095</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
+        <v>749341307.51009429</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
         <v>2029</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C39" s="10">
         <f t="shared" si="3"/>
-        <v>1421317065.71212</v>
-      </c>
-      <c r="D38" s="11">
+        <v>1421317065.7121234</v>
+      </c>
+      <c r="D39" s="10">
         <f t="shared" si="4"/>
-        <v>959425917.151283</v>
-      </c>
-      <c r="E38">
+        <v>959425917.15128326</v>
+      </c>
+      <c r="E39">
         <f t="shared" si="5"/>
-        <v>745673650.089779</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39">
+        <v>745673650.0897783</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40">
         <v>2030</v>
       </c>
-      <c r="B39">
+      <c r="B40">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C40" s="10">
         <f t="shared" si="3"/>
         <v>1419718880.5</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D40" s="10">
         <f t="shared" si="4"/>
         <v>953112984</v>
       </c>
-      <c r="E39">
+      <c r="E40">
         <f t="shared" si="5"/>
-        <v>740767186.941829</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40">
+        <v>740767186.94182909</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
         <v>2031</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C41" s="10">
         <f t="shared" si="3"/>
-        <v>1417701463.23684</v>
-      </c>
-      <c r="D40" s="11">
+        <v>1417701463.2368436</v>
+      </c>
+      <c r="D41" s="10">
         <f t="shared" si="4"/>
-        <v>945375053.580856</v>
-      </c>
-      <c r="E40">
+        <v>945375053.58085632</v>
+      </c>
+      <c r="E41">
         <f t="shared" si="5"/>
-        <v>734753204.291751</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41">
+        <v>734753204.29175043</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42">
         <v>2032</v>
       </c>
-      <c r="B41">
+      <c r="B42">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C42" s="10">
         <f t="shared" si="3"/>
-        <v>1415305468.60646</v>
-      </c>
-      <c r="D41" s="11">
+        <v>1415305468.6064639</v>
+      </c>
+      <c r="D42" s="10">
         <f t="shared" si="4"/>
-        <v>936437572.573181</v>
-      </c>
-      <c r="E41">
+        <v>936437572.57318115</v>
+      </c>
+      <c r="E42">
         <f t="shared" si="5"/>
-        <v>727806921.137978</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42">
+        <v>727806921.13797736</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
         <v>2033</v>
       </c>
-      <c r="B42">
+      <c r="B43">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C43" s="10">
         <f t="shared" si="3"/>
-        <v>1412568462.06595</v>
-      </c>
-      <c r="D42" s="11">
+        <v>1412568462.0659509</v>
+      </c>
+      <c r="D43" s="10">
         <f t="shared" si="4"/>
-        <v>926559351.045654</v>
-      </c>
-      <c r="E42">
+        <v>926559351.0456543</v>
+      </c>
+      <c r="E43">
         <f t="shared" si="5"/>
-        <v>720129486.777337</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43">
+        <v>720129486.77733684</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44">
         <v>2034</v>
       </c>
-      <c r="B43">
+      <c r="B44">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C44" s="10">
         <f t="shared" si="3"/>
-        <v>1409524248.56106</v>
-      </c>
-      <c r="D43" s="11">
+        <v>1409524248.5610561</v>
+      </c>
+      <c r="D44" s="10">
         <f t="shared" si="4"/>
-        <v>916012063.501053</v>
-      </c>
-      <c r="E43">
+        <v>916012063.50105286</v>
+      </c>
+      <c r="E44">
         <f t="shared" si="5"/>
-        <v>711932048.849788</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44">
+        <v>711932048.84978783</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>2035</v>
       </c>
-      <c r="B44">
+      <c r="B45">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C45" s="10">
         <f t="shared" si="3"/>
-        <v>1406202311.92969</v>
-      </c>
-      <c r="D44" s="11">
+        <v>1406202311.9296875</v>
+      </c>
+      <c r="D45" s="10">
         <f t="shared" si="4"/>
         <v>905062413.96875</v>
       </c>
-      <c r="E44">
+      <c r="E45">
         <f t="shared" si="5"/>
-        <v>703421891.90281</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45">
+        <v>703421891.90280938</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46">
         <v>2036</v>
       </c>
-      <c r="B45">
+      <c r="B46">
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C46" s="10">
         <f t="shared" si="3"/>
-        <v>1402627364.99354</v>
-      </c>
-      <c r="D45" s="11">
+        <v>1402627364.993536</v>
+      </c>
+      <c r="D46" s="10">
         <f t="shared" si="4"/>
-        <v>893956965.144592</v>
-      </c>
-      <c r="E45">
+        <v>893956965.14459229</v>
+      </c>
+      <c r="E46">
         <f t="shared" si="5"/>
-        <v>694790646.475145</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46">
+        <v>694790646.47514486</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47">
         <v>2037</v>
       </c>
-      <c r="B46">
+      <c r="B47">
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C47" s="10">
         <f t="shared" si="3"/>
-        <v>1398819010.33781</v>
-      </c>
-      <c r="D46" s="11">
+        <v>1398819010.3378115</v>
+      </c>
+      <c r="D47" s="10">
         <f t="shared" si="4"/>
-        <v>882909631.578293</v>
-      </c>
-      <c r="E46">
+        <v>882909631.57829285</v>
+      </c>
+      <c r="E47">
         <f t="shared" si="5"/>
-        <v>686204568.700009</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47">
+        <v>686204568.70000911</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48">
         <v>2038</v>
       </c>
-      <c r="B47">
+      <c r="B48">
         <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C48" s="10">
         <f t="shared" si="3"/>
-        <v>1394791511.7791</v>
-      </c>
-      <c r="D47" s="11">
+        <v>1394791511.7791042</v>
+      </c>
+      <c r="D48" s="10">
         <f t="shared" si="4"/>
-        <v>872091836.908539</v>
-      </c>
-      <c r="E47">
+        <v>872091836.90853882</v>
+      </c>
+      <c r="E48">
         <f t="shared" si="5"/>
-        <v>677796890.427915</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48">
+        <v>677796890.4279145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49">
         <v>2039</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C49" s="10">
         <f t="shared" si="3"/>
-        <v>1390553676.52136</v>
-      </c>
-      <c r="D48" s="11">
+        <v>1390553676.5213642</v>
+      </c>
+      <c r="D49" s="10">
         <f t="shared" si="4"/>
-        <v>861625335.145325</v>
-      </c>
-      <c r="E48">
+        <v>861625335.14532471</v>
+      </c>
+      <c r="E49">
         <f t="shared" si="5"/>
         <v>669662239.868734</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
-      <c r="A49">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
         <v>2040</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="C49" s="11">
+      <c r="C50" s="10">
         <f t="shared" si="3"/>
-        <v>1386108848</v>
-      </c>
-      <c r="D49" s="11">
+        <v>1386108847.999999</v>
+      </c>
+      <c r="D50" s="10">
         <f t="shared" si="4"/>
         <v>851577696</v>
       </c>
-      <c r="E49">
+      <c r="E50">
         <f t="shared" si="5"/>
-        <v>661853132.753382</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50">
+        <v>661853132.75338197</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
         <v>2041</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <f t="shared" si="2"/>
         <v>41</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C51" s="10">
         <f t="shared" si="3"/>
-        <v>1381455009.4141</v>
-      </c>
-      <c r="D50" s="11">
+        <v>1381455009.4141035</v>
+      </c>
+      <c r="D51" s="10">
         <f t="shared" si="4"/>
-        <v>841960454.262817</v>
-      </c>
-      <c r="E50">
+        <v>841960454.26281738</v>
+      </c>
+      <c r="E51">
         <f t="shared" si="5"/>
-        <v>654378534.014948</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51">
+        <v>654378534.01494718</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
         <v>2042</v>
       </c>
-      <c r="B51">
+      <c r="B52">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C52" s="10">
         <f t="shared" si="3"/>
-        <v>1376584997.94678</v>
-      </c>
-      <c r="D51" s="11">
+        <v>1376584997.9467831</v>
+      </c>
+      <c r="D52" s="10">
         <f t="shared" si="4"/>
-        <v>832729923.227905</v>
-      </c>
-      <c r="E51">
+        <v>832729923.22790527</v>
+      </c>
+      <c r="E52">
         <f t="shared" si="5"/>
-        <v>647204489.989217</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52">
+        <v>647204489.98921692</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53">
         <v>2043</v>
       </c>
-      <c r="B52">
+      <c r="B53">
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="C52" s="11">
+      <c r="C53" s="10">
         <f t="shared" si="3"/>
-        <v>1371486829.67363</v>
-      </c>
-      <c r="D52" s="11">
+        <v>1371486829.6736317</v>
+      </c>
+      <c r="D53" s="10">
         <f t="shared" si="4"/>
-        <v>823790672.165924</v>
-      </c>
-      <c r="E52">
+        <v>823790672.16592407</v>
+      </c>
+      <c r="E53">
         <f t="shared" si="5"/>
-        <v>640256831.134797</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53">
+        <v>640256831.13479662</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54">
         <v>2044</v>
       </c>
-      <c r="B53">
+      <c r="B54">
         <f t="shared" si="2"/>
         <v>44</v>
       </c>
-      <c r="C53" s="11">
+      <c r="C54" s="10">
         <f t="shared" si="3"/>
-        <v>1366144135.15929</v>
-      </c>
-      <c r="D53" s="11">
+        <v>1366144135.1592941</v>
+      </c>
+      <c r="D54" s="10">
         <f t="shared" si="4"/>
-        <v>815001667.844086</v>
-      </c>
-      <c r="E53">
+        <v>815001667.84408569</v>
+      </c>
+      <c r="E54">
         <f t="shared" si="5"/>
-        <v>633425945.272573</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54">
+        <v>633425945.27257252</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55">
         <v>2045</v>
       </c>
-      <c r="B54">
+      <c r="B55">
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="C54" s="11">
+      <c r="C55" s="10">
         <f t="shared" si="3"/>
-        <v>1360536705.74219</v>
-      </c>
-      <c r="D54" s="11">
+        <v>1360536705.7421875</v>
+      </c>
+      <c r="D55" s="10">
         <f t="shared" si="4"/>
         <v>806185080.09375</v>
       </c>
-      <c r="E54">
+      <c r="E55">
         <f t="shared" si="5"/>
-        <v>626573621.344687</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55">
+        <v>626573621.34468663</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56">
         <v>2046</v>
       </c>
-      <c r="B55">
+      <c r="B56">
         <f t="shared" si="2"/>
         <v>46</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C56" s="10">
         <f t="shared" si="3"/>
-        <v>1354641150.5073</v>
-      </c>
-      <c r="D55" s="11">
+        <v>1354641150.5072956</v>
+      </c>
+      <c r="D56" s="10">
         <f t="shared" si="4"/>
-        <v>797137751.425537</v>
-      </c>
-      <c r="E55">
+        <v>797137751.42553711</v>
+      </c>
+      <c r="E56">
         <f t="shared" si="5"/>
-        <v>619541963.692974</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56">
+        <v>619541963.69297397</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57">
         <v>2047</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="C56" s="11">
+      <c r="C57" s="10">
         <f t="shared" si="3"/>
-        <v>1348431663.94713</v>
-      </c>
-      <c r="D56" s="11">
+        <v>1348431663.9471321</v>
+      </c>
+      <c r="D57" s="10">
         <f t="shared" si="4"/>
-        <v>787645330.692017</v>
-      </c>
-      <c r="E56">
-        <f t="shared" si="5"/>
-        <v>612164376.856912</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57">
+        <v>787645330.6920166</v>
+      </c>
+      <c r="E57" s="10">
+        <f>D57*$B$75</f>
+        <v>612164376.8569119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58">
         <v>2048</v>
       </c>
-      <c r="B57">
+      <c r="B58">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C58" s="10">
         <f t="shared" si="3"/>
-        <v>1341880904.31078</v>
-      </c>
-      <c r="D57" s="11">
+        <v>1341880904.3107834</v>
+      </c>
+      <c r="D58" s="10">
         <f t="shared" si="4"/>
-        <v>777499070.797852</v>
-      </c>
-      <c r="E57">
+        <v>777499070.79785156</v>
+      </c>
+      <c r="E58">
         <f t="shared" si="5"/>
-        <v>604278620.890984</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58">
+        <v>604278620.89098394</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59">
         <v>2049</v>
       </c>
-      <c r="B58">
+      <c r="B59">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C59" s="10">
         <f t="shared" si="3"/>
-        <v>1334960982.6411</v>
-      </c>
-      <c r="D58" s="11">
+        <v>1334960982.6411018</v>
+      </c>
+      <c r="D59" s="10">
         <f t="shared" si="4"/>
-        <v>766515290.457397</v>
-      </c>
-      <c r="E58">
+        <v>766515290.45739746</v>
+      </c>
+      <c r="E59">
         <f t="shared" si="5"/>
-        <v>595741937.201462</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59">
+        <v>595741937.2014612</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60">
         <v>2050</v>
       </c>
-      <c r="B59">
+      <c r="B60">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="C59" s="11">
+      <c r="C60" s="10">
         <f t="shared" si="3"/>
         <v>1327644562.5</v>
       </c>
-      <c r="D59" s="11">
+      <c r="D60" s="10">
         <f t="shared" si="4"/>
         <v>754557500</v>
       </c>
-      <c r="E59">
+      <c r="E60">
         <f t="shared" si="5"/>
-        <v>586448244.902788</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60">
+        <v>586448244.90278816</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61">
         <v>2051</v>
       </c>
-      <c r="B60">
+      <c r="B61">
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="C60" s="11">
+      <c r="C61" s="10">
         <f t="shared" si="3"/>
-        <v>1319906070.38186</v>
-      </c>
-      <c r="D60" s="11">
+        <v>1319906070.3818645</v>
+      </c>
+      <c r="D61" s="10">
         <f t="shared" si="4"/>
-        <v>741561191.222839</v>
-      </c>
-      <c r="E60">
+        <v>741561191.22283936</v>
+      </c>
+      <c r="E61">
         <f t="shared" si="5"/>
-        <v>576347407.693456</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61">
+        <v>576347407.69345605</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62">
         <v>2052</v>
       </c>
-      <c r="B61">
+      <c r="B62">
         <f t="shared" si="2"/>
         <v>52</v>
       </c>
-      <c r="C61" s="11">
+      <c r="C62" s="10">
         <f t="shared" si="3"/>
-        <v>1311723016.8151</v>
-      </c>
-      <c r="D61" s="11">
+        <v>1311723016.8151016</v>
+      </c>
+      <c r="D62" s="10">
         <f t="shared" si="4"/>
-        <v>727561291.290649</v>
-      </c>
-      <c r="E61">
+        <v>727561291.29064941</v>
+      </c>
+      <c r="E62">
         <f t="shared" si="5"/>
-        <v>565466571.250843</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62">
+        <v>565466571.25084245</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63">
         <v>2053</v>
       </c>
-      <c r="B62">
+      <c r="B63">
         <f t="shared" si="2"/>
         <v>53</v>
       </c>
-      <c r="C62" s="11">
+      <c r="C63" s="10">
         <f t="shared" si="3"/>
-        <v>1303077428.15181</v>
-      </c>
-      <c r="D62" s="11">
+        <v>1303077428.1518135</v>
+      </c>
+      <c r="D63" s="10">
         <f t="shared" si="4"/>
-        <v>712722280.684204</v>
-      </c>
-      <c r="E62">
+        <v>712722280.6842041</v>
+      </c>
+      <c r="E63">
         <f t="shared" si="5"/>
-        <v>553933571.146485</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63">
+        <v>553933571.14648497</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64">
         <v>2054</v>
       </c>
-      <c r="B63">
+      <c r="B64">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="C63" s="11">
+      <c r="C64" s="10">
         <f t="shared" si="3"/>
-        <v>1293957389.04554</v>
-      </c>
-      <c r="D63" s="11">
+        <v>1293957389.045536</v>
+      </c>
+      <c r="D64" s="10">
         <f t="shared" si="4"/>
-        <v>697370975.195129</v>
-      </c>
-      <c r="E63">
+        <v>697370975.19512939</v>
+      </c>
+      <c r="E64">
         <f t="shared" si="5"/>
-        <v>542002411.279895</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64">
+        <v>542002411.27989507</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65">
         <v>2055</v>
       </c>
-      <c r="B64">
+      <c r="B65">
         <f t="shared" si="2"/>
         <v>55</v>
       </c>
-      <c r="C64" s="11">
+      <c r="C65" s="10">
         <f t="shared" si="3"/>
-        <v>1284358695.61718</v>
-      </c>
-      <c r="D64" s="11">
+        <v>1284358695.6171837</v>
+      </c>
+      <c r="D65" s="10">
         <f t="shared" si="4"/>
         <v>682031971.96875</v>
       </c>
-      <c r="E64">
+      <c r="E65">
         <f t="shared" si="5"/>
-        <v>530080812.832238</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65">
+        <v>530080812.83223748</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66">
         <v>2056</v>
       </c>
-      <c r="B65">
+      <c r="B66">
         <f t="shared" si="2"/>
         <v>56</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C66" s="10">
         <f t="shared" si="3"/>
-        <v>1274286619.30905</v>
-      </c>
-      <c r="D65" s="11">
+        <v>1274286619.3090515</v>
+      </c>
+      <c r="D66" s="10">
         <f t="shared" si="4"/>
-        <v>667465759.594482</v>
-      </c>
-      <c r="E65">
+        <v>667465759.59448242</v>
+      </c>
+      <c r="E66">
         <f t="shared" si="5"/>
-        <v>518759833.739497</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66">
+        <v>518759833.73949701</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67">
         <v>2057</v>
       </c>
-      <c r="B66">
+      <c r="B67">
         <f t="shared" si="2"/>
         <v>57</v>
       </c>
-      <c r="C66" s="11">
+      <c r="C67" s="10">
         <f t="shared" si="3"/>
-        <v>1263757781.42695</v>
-      </c>
-      <c r="D66" s="11">
+        <v>1263757781.4269485</v>
+      </c>
+      <c r="D67" s="10">
         <f t="shared" si="4"/>
-        <v>654709492.243774</v>
-      </c>
-      <c r="E66">
+        <v>654709492.24377441</v>
+      </c>
+      <c r="E67">
         <f t="shared" si="5"/>
-        <v>508845558.685133</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67">
+        <v>508845558.6851328</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68">
         <v>2058</v>
       </c>
-      <c r="B67">
+      <c r="B68">
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C68" s="10">
         <f t="shared" si="3"/>
-        <v>1252802138.37046</v>
-      </c>
-      <c r="D67" s="11">
+        <v>1252802138.3704605</v>
+      </c>
+      <c r="D68" s="10">
         <f t="shared" si="4"/>
-        <v>645120427.855103</v>
-      </c>
-      <c r="E67">
+        <v>645120427.85510254</v>
+      </c>
+      <c r="E68">
         <f t="shared" si="5"/>
-        <v>501392859.61184</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68">
+        <v>501392859.61183953</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69">
         <v>2059</v>
       </c>
-      <c r="B68">
+      <c r="B69">
         <f t="shared" si="2"/>
         <v>59</v>
       </c>
-      <c r="C68" s="11">
+      <c r="C69" s="10">
         <f t="shared" si="3"/>
-        <v>1241465077.55134</v>
-      </c>
-      <c r="D68" s="11">
+        <v>1241465077.5513382</v>
+      </c>
+      <c r="D69" s="10">
         <f t="shared" si="4"/>
-        <v>640422030.367432</v>
-      </c>
-      <c r="E68">
+        <v>640422030.36743164</v>
+      </c>
+      <c r="E69">
         <f t="shared" si="5"/>
-        <v>497741226.753509</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69">
+        <v>497741226.75350833</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70">
         <v>2060</v>
       </c>
-      <c r="B69">
+      <c r="B70">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C70" s="10">
         <f t="shared" si="3"/>
         <v>1229809624</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D70" s="10">
         <f t="shared" si="4"/>
         <v>642752736</v>
       </c>
-      <c r="E69">
+      <c r="E70">
         <f t="shared" si="5"/>
-        <v>499552670.185725</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" t="s">
-        <v>59</v>
-      </c>
-      <c r="B71" s="11">
-        <v>965815904</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" t="s">
-        <v>60</v>
-      </c>
-      <c r="B72">
-        <v>750640000</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" t="s">
-        <v>61</v>
+        <v>499552670.18572491</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B72" s="10">
+        <v>972809418.79524612</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="21" t="s">
+        <v>95</v>
       </c>
       <c r="B73">
-        <f>B72/B71</f>
+        <v>756075416.75402272</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" s="10">
+        <f>B73/B72</f>
         <v>0.777208158295144</v>
       </c>
     </row>
-    <row r="74" spans="2:2">
-      <c r="B74">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B75">
         <v>0.777208158295144</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:O43"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.625"/>
-    <col min="5" max="5" width="12.625"/>
-    <col min="7" max="7" width="12.625"/>
-    <col min="9" max="9" width="12.625"/>
-    <col min="12" max="12" width="12.625"/>
-    <col min="15" max="15" width="12.625"/>
+    <col min="3" max="3" width="12.6640625"/>
+    <col min="5" max="5" width="12.6640625"/>
+    <col min="7" max="7" width="12.6640625"/>
+    <col min="9" max="9" width="12.6640625"/>
+    <col min="12" max="12" width="12.6640625"/>
+    <col min="15" max="15" width="12.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>56</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
       </c>
       <c r="L1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="9">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A2" s="8">
         <v>2010</v>
       </c>
       <c r="B2">
@@ -6066,31 +5579,31 @@
       </c>
       <c r="G2">
         <f>B12*B14/B11</f>
-        <v>1.07724575473044</v>
+        <v>1.077245754730443</v>
       </c>
       <c r="H2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="I2">
-        <v>97379</v>
+        <v>90501</v>
       </c>
       <c r="K2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="L2">
         <f>I2*就业人口计算!E29</f>
-        <v>73096572560000</v>
+        <v>68425581291655.813</v>
       </c>
       <c r="N2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="O2">
-        <f>L2*汇率!B22</f>
-        <v>10061792771500.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="9">
+        <f>L2*汇率!B21</f>
+        <v>9477713619655.707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A3" s="8">
         <v>2011</v>
       </c>
       <c r="B3">
@@ -6098,39 +5611,38 @@
       </c>
       <c r="C3">
         <f>B3/B2-1</f>
-        <v>0.177518826278889</v>
+        <v>0.17751882627888871</v>
       </c>
       <c r="D3">
         <v>41799</v>
       </c>
       <c r="E3">
         <f>D3/D2-1</f>
-        <v>0.143955773283341</v>
+        <v>0.14395577328334119</v>
       </c>
       <c r="H3">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="I3">
-        <f>I2*$G$2</f>
-        <v>104901.114349896</v>
+        <v>97379</v>
       </c>
       <c r="K3">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="L3">
         <f>I3*就业人口计算!E30</f>
-        <v>78545390358218.8</v>
+        <v>73096572559999.969</v>
       </c>
       <c r="N3">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="O3">
-        <f>L3*汇率!B23</f>
-        <v>10579086336261.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="9">
+        <f>L3*汇率!B22</f>
+        <v>10061792771500.137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A4" s="8">
         <v>2012</v>
       </c>
       <c r="B4">
@@ -6138,39 +5650,39 @@
       </c>
       <c r="C4">
         <f t="shared" ref="C4:C12" si="0">B4/B3-1</f>
-        <v>0.0963144692229236</v>
+        <v>9.6314469222923638E-2</v>
       </c>
       <c r="D4">
         <v>46769</v>
       </c>
       <c r="E4">
         <f>D4/D3-1</f>
-        <v>0.118902366085313</v>
+        <v>0.11890236608531302</v>
       </c>
       <c r="H4">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I15" si="1">I3*$G$2</f>
-        <v>113004.280099918</v>
+        <f>I3*$G$2</f>
+        <v>104901.11434989581</v>
       </c>
       <c r="K4">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="L4">
         <f>I4*就业人口计算!E31</f>
-        <v>84641226914503.5</v>
+        <v>78545390358218.766</v>
       </c>
       <c r="N4">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="O4">
-        <f>L4*汇率!B24</f>
-        <v>11154715888934</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="9">
+        <f>L4*汇率!B23</f>
+        <v>10579086336261.557</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A5" s="8">
         <v>2013</v>
       </c>
       <c r="B5">
@@ -6178,39 +5690,39 @@
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
-        <v>0.0936863543788187</v>
+        <v>9.368635437881867E-2</v>
       </c>
       <c r="D5">
         <v>51483</v>
       </c>
       <c r="E5">
         <f>D5/D4-1</f>
-        <v>0.100793260493062</v>
+        <v>0.1007932604930617</v>
       </c>
       <c r="H5">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="I5">
-        <f t="shared" si="1"/>
-        <v>121733.381004007</v>
+        <f t="shared" ref="I5:I16" si="1">I4*$G$2</f>
+        <v>113004.28009991802</v>
       </c>
       <c r="K5">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="L5">
         <f>I5*就业人口计算!E32</f>
-        <v>91334231366052.1</v>
+        <v>84641226914503.5</v>
       </c>
       <c r="N5">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="O5">
-        <f>L5*汇率!B25</f>
-        <v>11777666314251.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="9">
+        <f>L5*汇率!B24</f>
+        <v>11154715888934.023</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A6" s="8">
         <v>2014</v>
       </c>
       <c r="B6">
@@ -6218,39 +5730,39 @@
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
-        <v>0.0785111616893119</v>
+        <v>7.8511161689311937E-2</v>
       </c>
       <c r="D6">
         <v>56360</v>
       </c>
       <c r="E6">
         <f t="shared" ref="E6:E12" si="2">D6/D5-1</f>
-        <v>0.0947302993221064</v>
+        <v>9.4730299322106415E-2</v>
       </c>
       <c r="H6">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
-        <v>131136.76789555</v>
+        <v>121733.38100400657</v>
       </c>
       <c r="K6">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="L6">
         <f>I6*就业人口计算!E33</f>
-        <v>98577851142514.1</v>
+        <v>91334231366052</v>
       </c>
       <c r="N6">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="O6">
-        <f>L6*汇率!B26</f>
-        <v>12438102130933.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="9">
+        <f>L6*汇率!B25</f>
+        <v>11777666314251.479</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A7" s="8">
         <v>2015</v>
       </c>
       <c r="B7">
@@ -6258,39 +5770,39 @@
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>0.0641626875852661</v>
+        <v>6.4162687585266109E-2</v>
       </c>
       <c r="D7">
         <v>62029</v>
       </c>
       <c r="E7">
         <f t="shared" si="2"/>
-        <v>0.100585521646558</v>
+        <v>0.10058552164655787</v>
       </c>
       <c r="H7">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="I7">
         <f t="shared" si="1"/>
-        <v>141266.526504552</v>
+        <v>131136.76789554965</v>
       </c>
       <c r="K7">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="L7">
         <f>I7*就业人口计算!E34</f>
-        <v>106330410571745</v>
+        <v>98577851142513.938</v>
       </c>
       <c r="N7">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="O7">
-        <f>L7*汇率!B27</f>
-        <v>13127480040440.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="9">
+        <f>L7*汇率!B26</f>
+        <v>12438102130933.826</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A8" s="8">
         <v>2016</v>
       </c>
       <c r="B8">
@@ -6298,39 +5810,39 @@
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
-        <v>0.0773406514162094</v>
+        <v>7.7340651416209383E-2</v>
       </c>
       <c r="D8">
         <v>67569</v>
       </c>
       <c r="E8">
         <f t="shared" si="2"/>
-        <v>0.0893130632446113</v>
+        <v>8.9313063244611302E-2</v>
       </c>
       <c r="H8">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>152178.765962545</v>
+        <v>141266.52650455231</v>
       </c>
       <c r="K8">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="L8">
         <f>I8*就业人口计算!E35</f>
-        <v>114556710303993</v>
+        <v>106330410571744.86</v>
       </c>
       <c r="N8">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="O8">
-        <f>L8*汇率!B28</f>
-        <v>13838643248878.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="9">
+        <f>L8*汇率!B27</f>
+        <v>13127480040440.092</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A9" s="8">
         <v>2017</v>
       </c>
       <c r="B9">
@@ -6338,39 +5850,39 @@
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>0.108008106650801</v>
+        <v>0.10800810665080052</v>
       </c>
       <c r="D9">
         <v>74318</v>
       </c>
       <c r="E9">
         <f t="shared" si="2"/>
-        <v>0.0998830824786514</v>
+        <v>9.9883082478651408E-2</v>
       </c>
       <c r="H9">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="I9">
         <f t="shared" si="1"/>
-        <v>163933.929593269</v>
+        <v>152178.7659625446</v>
       </c>
       <c r="K9">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="L9">
         <f>I9*就业人口计算!E36</f>
-        <v>123229606799130</v>
+        <v>114556710303992.52</v>
       </c>
       <c r="N9">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="O9">
-        <f>L9*汇率!B29</f>
-        <v>14565894060916.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="9">
+        <f>L9*汇率!B28</f>
+        <v>13838643248878.334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A10" s="8">
         <v>2018</v>
       </c>
       <c r="B10">
@@ -6378,39 +5890,39 @@
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
-        <v>0.0997113706537791</v>
+        <v>9.9711370653779108E-2</v>
       </c>
       <c r="D10">
         <v>82413</v>
       </c>
       <c r="E10">
         <f t="shared" si="2"/>
-        <v>0.10892381388089</v>
+        <v>0.10892381388089012</v>
       </c>
       <c r="H10">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="I10">
         <f t="shared" si="1"/>
-        <v>176597.129710628</v>
+        <v>163933.92959326881</v>
       </c>
       <c r="K10">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="L10">
         <f>I10*就业人口计算!E37</f>
-        <v>132331524079892</v>
+        <v>123229606799129.72</v>
       </c>
       <c r="N10">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="O10">
-        <f>L10*汇率!B30</f>
-        <v>15305041191632.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="9">
+        <f>L10*汇率!B29</f>
+        <v>14565894060916.844</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A11" s="8">
         <v>2019</v>
       </c>
       <c r="B11">
@@ -6418,39 +5930,39 @@
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
-        <v>0.0693380535294656</v>
+        <v>6.9338053529465649E-2</v>
       </c>
       <c r="D11">
         <v>90501</v>
       </c>
       <c r="E11">
         <f t="shared" si="2"/>
-        <v>0.0981398565760256</v>
+        <v>9.8139856576025641E-2</v>
       </c>
       <c r="H11">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="I11">
         <f t="shared" si="1"/>
-        <v>190238.508278356</v>
+        <v>176597.12971062819</v>
       </c>
       <c r="K11">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="L11">
         <f>I11*就业人口计算!E38</f>
-        <v>141855842855556</v>
+        <v>132331524079891.84</v>
       </c>
       <c r="N11">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="O11">
-        <f>L11*汇率!B31</f>
-        <v>16053418263175.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="9">
+        <f>L11*汇率!B30</f>
+        <v>15305041191632.883</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A12" s="8">
         <v>2020</v>
       </c>
       <c r="B12">
@@ -6458,2106 +5970,2152 @@
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
-        <v>0.0249721738634094</v>
+        <v>2.4972173863409441E-2</v>
       </c>
       <c r="D12">
         <v>97379</v>
       </c>
       <c r="E12">
         <f t="shared" si="2"/>
-        <v>0.0759991602302736</v>
+        <v>7.5999160230273644E-2</v>
       </c>
       <c r="H12">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
-        <v>204933.625429111</v>
+        <v>190238.50827835561</v>
       </c>
       <c r="K12">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="L12">
         <f>I12*就业人口计算!E39</f>
-        <v>151808105218913</v>
+        <v>141855842855555.94</v>
       </c>
       <c r="N12">
+        <v>2029</v>
+      </c>
+      <c r="O12">
+        <f>L12*汇率!B31</f>
+        <v>16053418263175.684</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H13">
         <v>2030</v>
-      </c>
-      <c r="O12">
-        <f>L12*汇率!B32</f>
-        <v>16809870066079.2</v>
-      </c>
-    </row>
-    <row r="13" spans="8:15">
-      <c r="H13">
-        <v>2031</v>
       </c>
       <c r="I13">
         <f t="shared" si="1"/>
-        <v>220763.877995028</v>
+        <v>204933.62542911083</v>
       </c>
       <c r="K13">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="L13">
         <f>I13*就业人口计算!E40</f>
-        <v>162206966748720</v>
+        <v>151808105218912.94</v>
       </c>
       <c r="N13">
+        <v>2030</v>
+      </c>
+      <c r="O13">
+        <f>L13*汇率!B32</f>
+        <v>16809870066079.166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="H14">
         <v>2031</v>
-      </c>
-      <c r="O13">
-        <f>L13*汇率!B33</f>
-        <v>17574703391078</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15">
-      <c r="B14">
-        <v>1.051</v>
-      </c>
-      <c r="H14">
-        <v>2032</v>
       </c>
       <c r="I14">
         <f t="shared" si="1"/>
-        <v>237816.950367974</v>
+        <v>220763.87799502842</v>
       </c>
       <c r="K14">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="L14">
         <f>I14*就业人口计算!E41</f>
-        <v>173084822441738</v>
+        <v>162206966748720.19</v>
       </c>
       <c r="N14">
+        <v>2031</v>
+      </c>
+      <c r="O14">
+        <f>L14*汇率!B33</f>
+        <v>17574703391078.051</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H15">
         <v>2032</v>
-      </c>
-      <c r="O14">
-        <f>L14*汇率!B34</f>
-        <v>18349599600685.8</v>
-      </c>
-    </row>
-    <row r="15" spans="8:15">
-      <c r="H15">
-        <v>2033</v>
       </c>
       <c r="I15">
         <f t="shared" si="1"/>
-        <v>256187.30018684</v>
+        <v>237816.95036797383</v>
       </c>
       <c r="K15">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="L15">
         <f>I15*就业人口计算!E42</f>
-        <v>184488029002421</v>
+        <v>173084822441738.19</v>
       </c>
       <c r="N15">
+        <v>2032</v>
+      </c>
+      <c r="O15">
+        <f>L15*汇率!B34</f>
+        <v>18349599600685.863</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H16">
         <v>2033</v>
       </c>
-      <c r="O15">
-        <f>L15*汇率!B35</f>
-        <v>19137486638604.6</v>
-      </c>
-    </row>
-    <row r="16" spans="8:15">
-      <c r="H16">
-        <v>2034</v>
-      </c>
       <c r="I16">
-        <f t="shared" ref="I16:I42" si="3">I15*$G$2</f>
-        <v>275976.681542127</v>
+        <f t="shared" si="1"/>
+        <v>256187.30018684026</v>
       </c>
       <c r="K16">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="L16">
         <f>I16*就业人口计算!E43</f>
-        <v>196476644325052</v>
+        <v>184488029002420.81</v>
       </c>
       <c r="N16">
+        <v>2033</v>
+      </c>
+      <c r="O16">
+        <f>L16*汇率!B35</f>
+        <v>19137486638604.605</v>
+      </c>
+    </row>
+    <row r="17" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H17">
         <v>2034</v>
       </c>
-      <c r="O16">
-        <f>L16*汇率!B36</f>
-        <v>19942368901402.2</v>
-      </c>
-    </row>
-    <row r="17" spans="8:15">
-      <c r="H17">
-        <v>2035</v>
-      </c>
       <c r="I17">
-        <f t="shared" si="3"/>
-        <v>297294.708595852</v>
+        <f t="shared" ref="I17:I43" si="3">I16*$G$2</f>
+        <v>275976.68154212733</v>
       </c>
       <c r="K17">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="L17">
         <f>I17*就业人口计算!E44</f>
-        <v>209123606373189</v>
+        <v>196476644325052.13</v>
       </c>
       <c r="N17">
+        <v>2034</v>
+      </c>
+      <c r="O17">
+        <f>L17*汇率!B36</f>
+        <v>19942368901402.176</v>
+      </c>
+    </row>
+    <row r="18" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H18">
         <v>2035</v>
-      </c>
-      <c r="O17">
-        <f>L17*汇率!B37</f>
-        <v>20769114357701.5</v>
-      </c>
-    </row>
-    <row r="18" spans="8:15">
-      <c r="H18">
-        <v>2036</v>
       </c>
       <c r="I18">
         <f t="shared" si="3"/>
-        <v>320259.462738706</v>
+        <v>297294.70859585208</v>
       </c>
       <c r="K18">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="L18">
         <f>I18*就业人口计算!E45</f>
-        <v>222513279156008</v>
+        <v>209123606373188.69</v>
       </c>
       <c r="N18">
+        <v>2035</v>
+      </c>
+      <c r="O18">
+        <f>L18*汇率!B37</f>
+        <v>20769114357701.492</v>
+      </c>
+    </row>
+    <row r="19" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H19">
         <v>2036</v>
-      </c>
-      <c r="O18">
-        <f>L18*汇率!B38</f>
-        <v>21623199537405.6</v>
-      </c>
-    </row>
-    <row r="19" spans="8:15">
-      <c r="H19">
-        <v>2037</v>
       </c>
       <c r="I19">
         <f t="shared" si="3"/>
-        <v>344998.146647523</v>
+        <v>320259.4627387058</v>
       </c>
       <c r="K19">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="L19">
         <f>I19*就业人口计算!E46</f>
-        <v>236739304422566</v>
+        <v>222513279156007.97</v>
       </c>
       <c r="N19">
+        <v>2036</v>
+      </c>
+      <c r="O19">
+        <f>L19*汇率!B38</f>
+        <v>21623199537405.582</v>
+      </c>
+    </row>
+    <row r="20" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H20">
         <v>2037</v>
-      </c>
-      <c r="O19">
-        <f>L19*汇率!B39</f>
-        <v>22510414575272.3</v>
-      </c>
-    </row>
-    <row r="20" spans="8:15">
-      <c r="H20">
-        <v>2038</v>
       </c>
       <c r="I20">
         <f t="shared" si="3"/>
-        <v>371647.788865915</v>
+        <v>344998.14664752333</v>
       </c>
       <c r="K20">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="L20">
         <f>I20*就业人口计算!E47</f>
-        <v>251901715627728</v>
+        <v>236739304422566.25</v>
       </c>
       <c r="N20">
+        <v>2037</v>
+      </c>
+      <c r="O20">
+        <f>L20*汇率!B39</f>
+        <v>22510414575272.332</v>
+      </c>
+    </row>
+    <row r="21" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H21">
         <v>2038</v>
-      </c>
-      <c r="O20">
-        <f>L20*汇率!B40</f>
-        <v>23436532433989.2</v>
-      </c>
-    </row>
-    <row r="21" spans="8:15">
-      <c r="H21">
-        <v>2039</v>
       </c>
       <c r="I21">
         <f t="shared" si="3"/>
-        <v>400356.002810763</v>
+        <v>371647.78886591533</v>
       </c>
       <c r="K21">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="L21">
         <f>I21*就业人口计算!E48</f>
-        <v>268103297587149</v>
+        <v>251901715627727.5</v>
       </c>
       <c r="N21">
+        <v>2038</v>
+      </c>
+      <c r="O21">
+        <f>L21*汇率!B40</f>
+        <v>23436532433989.188</v>
+      </c>
+    </row>
+    <row r="22" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H22">
         <v>2039</v>
-      </c>
-      <c r="O21">
-        <f>L21*汇率!B41</f>
-        <v>24406948813717.5</v>
-      </c>
-    </row>
-    <row r="22" spans="8:15">
-      <c r="H22">
-        <v>2040</v>
       </c>
       <c r="I22">
         <f t="shared" si="3"/>
-        <v>431281.804408744</v>
+        <v>400356.00281076331</v>
       </c>
       <c r="K22">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="L22">
         <f>I22*就业人口计算!E49</f>
-        <v>285445213347459</v>
+        <v>268103297587148.94</v>
       </c>
       <c r="N22">
+        <v>2039</v>
+      </c>
+      <c r="O22">
+        <f>L22*汇率!B41</f>
+        <v>24406948813717.52</v>
+      </c>
+    </row>
+    <row r="23" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H23">
         <v>2040</v>
-      </c>
-      <c r="O22">
-        <f>L22*汇率!B42</f>
-        <v>25426302148134.8</v>
-      </c>
-    </row>
-    <row r="23" spans="8:15">
-      <c r="H23">
-        <v>2041</v>
       </c>
       <c r="I23">
         <f t="shared" si="3"/>
-        <v>464596.492891805</v>
+        <v>431281.80440874409</v>
       </c>
       <c r="K23">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="L23">
         <f>I23*就业人口计算!E50</f>
-        <v>304021971927025</v>
+        <v>285445213347458.63</v>
       </c>
       <c r="N23">
+        <v>2040</v>
+      </c>
+      <c r="O23">
+        <f>L23*汇率!B42</f>
+        <v>25426302148134.738</v>
+      </c>
+    </row>
+    <row r="24" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H24">
         <v>2041</v>
-      </c>
-      <c r="O23">
-        <f>L23*汇率!B43</f>
-        <v>26498086570621.1</v>
-      </c>
-    </row>
-    <row r="24" spans="8:15">
-      <c r="H24">
-        <v>2042</v>
       </c>
       <c r="I24">
         <f t="shared" si="3"/>
-        <v>500484.599630349</v>
+        <v>464596.49289180484</v>
       </c>
       <c r="K24">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="L24">
         <f>I24*就业人口计算!E51</f>
-        <v>323915880051218</v>
+        <v>304021971927025.06</v>
       </c>
       <c r="N24">
+        <v>2041</v>
+      </c>
+      <c r="O24">
+        <f>L24*汇率!B43</f>
+        <v>26498086570621.102</v>
+      </c>
+    </row>
+    <row r="25" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H25">
         <v>2042</v>
-      </c>
-      <c r="O24">
-        <f>L24*汇率!B44</f>
-        <v>27624274898147.9</v>
-      </c>
-    </row>
-    <row r="25" spans="8:15">
-      <c r="H25">
-        <v>2043</v>
       </c>
       <c r="I25">
         <f t="shared" si="3"/>
-        <v>539144.910259759</v>
+        <v>500484.5996303492</v>
       </c>
       <c r="K25">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="L25">
         <f>I25*就业人口计算!E52</f>
-        <v>345191211765368</v>
+        <v>323915880051217.56</v>
       </c>
       <c r="N25">
+        <v>2042</v>
+      </c>
+      <c r="O25">
+        <f>L25*汇率!B44</f>
+        <v>27624274898147.832</v>
+      </c>
+    </row>
+    <row r="26" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H26">
         <v>2043</v>
-      </c>
-      <c r="O25">
-        <f>L25*汇率!B45</f>
-        <v>28804973625731.7</v>
-      </c>
-    </row>
-    <row r="26" spans="8:15">
-      <c r="H26">
-        <v>2044</v>
       </c>
       <c r="I26">
         <f t="shared" si="3"/>
-        <v>580791.565761851</v>
+        <v>539144.91025975917</v>
       </c>
       <c r="K26">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="L26">
         <f>I26*就业人口计算!E53</f>
-        <v>367888446549038</v>
+        <v>345191211765367.69</v>
       </c>
       <c r="N26">
+        <v>2043</v>
+      </c>
+      <c r="O26">
+        <f>L26*汇率!B45</f>
+        <v>28804973625731.707</v>
+      </c>
+    </row>
+    <row r="27" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H27">
         <v>2044</v>
-      </c>
-      <c r="O26">
-        <f>L26*汇率!B46</f>
-        <v>30038137764849.7</v>
-      </c>
-    </row>
-    <row r="27" spans="8:15">
-      <c r="H27">
-        <v>2045</v>
       </c>
       <c r="I27">
         <f t="shared" si="3"/>
-        <v>625655.248600201</v>
+        <v>580791.56576185126</v>
       </c>
       <c r="K27">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="L27">
         <f>I27*就业人口计算!E54</f>
-        <v>392019074828738</v>
+        <v>367888446549038.13</v>
       </c>
       <c r="N27">
+        <v>2044</v>
+      </c>
+      <c r="O27">
+        <f>L27*汇率!B46</f>
+        <v>30038137764849.738</v>
+      </c>
+    </row>
+    <row r="28" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H28">
         <v>2045</v>
-      </c>
-      <c r="O27">
-        <f>L27*汇率!B47</f>
-        <v>31319380223052.7</v>
-      </c>
-    </row>
-    <row r="28" spans="8:15">
-      <c r="H28">
-        <v>2046</v>
       </c>
       <c r="I28">
         <f t="shared" si="3"/>
-        <v>673984.460479387</v>
+        <v>625655.24860020122</v>
       </c>
       <c r="K28">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="L28">
         <f>I28*就业人口计算!E55</f>
-        <v>417561656143949</v>
+        <v>392019074828738.25</v>
       </c>
       <c r="N28">
+        <v>2045</v>
+      </c>
+      <c r="O28">
+        <f>L28*汇率!B47</f>
+        <v>31319380223052.77</v>
+      </c>
+    </row>
+    <row r="29" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H29">
         <v>2046</v>
-      </c>
-      <c r="O28">
-        <f>L28*汇率!B48</f>
-        <v>32641918452907.7</v>
-      </c>
-    </row>
-    <row r="29" spans="8:15">
-      <c r="H29">
-        <v>2047</v>
       </c>
       <c r="I29">
         <f t="shared" si="3"/>
-        <v>726046.898805707</v>
+        <v>673984.46047938673</v>
       </c>
       <c r="K29">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="L29">
         <f>I29*就业人口计算!E56</f>
-        <v>444460047376289</v>
+        <v>417561656143948.88</v>
       </c>
       <c r="N29">
+        <v>2046</v>
+      </c>
+      <c r="O29">
+        <f>L29*汇率!B48</f>
+        <v>32641918452907.676</v>
+      </c>
+    </row>
+    <row r="30" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H30">
         <v>2047</v>
-      </c>
-      <c r="O29">
-        <f>L29*汇率!B49</f>
-        <v>33996710457655.9</v>
-      </c>
-    </row>
-    <row r="30" spans="8:15">
-      <c r="H30">
-        <v>2048</v>
       </c>
       <c r="I30">
         <f t="shared" si="3"/>
-        <v>782130.939473652</v>
+        <v>726046.89880570746</v>
       </c>
       <c r="K30">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="L30">
         <f>I30*就业人口计算!E57</f>
-        <v>472625005461308</v>
+        <v>444460047376289.25</v>
       </c>
       <c r="N30">
+        <v>2047</v>
+      </c>
+      <c r="O30">
+        <f>L30*汇率!B49</f>
+        <v>33996710457655.945</v>
+      </c>
+    </row>
+    <row r="31" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H31">
         <v>2048</v>
-      </c>
-      <c r="O30">
-        <f>L30*汇率!B50</f>
-        <v>35372843109278.8</v>
-      </c>
-    </row>
-    <row r="31" spans="8:15">
-      <c r="H31">
-        <v>2049</v>
       </c>
       <c r="I31">
         <f t="shared" si="3"/>
-        <v>842547.234191325</v>
+        <v>782130.93947365193</v>
       </c>
       <c r="K31">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="L31">
         <f>I31*就业人口计算!E58</f>
-        <v>501940721480874</v>
+        <v>472625005461308</v>
       </c>
       <c r="N31">
+        <v>2048</v>
+      </c>
+      <c r="O31">
+        <f>L31*汇率!B50</f>
+        <v>35372843109278.789</v>
+      </c>
+    </row>
+    <row r="32" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H32">
         <v>2049</v>
-      </c>
-      <c r="O31">
-        <f>L31*汇率!B51</f>
-        <v>36758248314259.7</v>
-      </c>
-    </row>
-    <row r="32" spans="8:15">
-      <c r="H32">
-        <v>2050</v>
       </c>
       <c r="I32">
         <f t="shared" si="3"/>
-        <v>907630.431192481</v>
+        <v>842547.23419132468</v>
       </c>
       <c r="K32">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="L32">
         <f>I32*就业人口计算!E59</f>
-        <v>532278273393191</v>
+        <v>501940721480872.94</v>
       </c>
       <c r="N32">
+        <v>2049</v>
+      </c>
+      <c r="O32">
+        <f>L32*汇率!B51</f>
+        <v>36758248314259.617</v>
+      </c>
+    </row>
+    <row r="33" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H33">
         <v>2050</v>
-      </c>
-      <c r="O32">
-        <f>L32*汇率!B52</f>
-        <v>38140837079322.8</v>
-      </c>
-    </row>
-    <row r="33" spans="8:15">
-      <c r="H33">
-        <v>2051</v>
       </c>
       <c r="I33">
         <f t="shared" si="3"/>
-        <v>977741.028866261</v>
+        <v>907630.43119248084</v>
       </c>
       <c r="K33">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="L33">
         <f>I33*就业人口计算!E60</f>
-        <v>563518507382602</v>
+        <v>532278273393191.25</v>
       </c>
       <c r="N33">
+        <v>2050</v>
+      </c>
+      <c r="O33">
+        <f>L33*汇率!B52</f>
+        <v>38140837079322.844</v>
+      </c>
+    </row>
+    <row r="34" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H34">
         <v>2051</v>
-      </c>
-      <c r="O33">
-        <f>L33*汇率!B53</f>
-        <v>39510158236278.4</v>
-      </c>
-    </row>
-    <row r="34" spans="8:15">
-      <c r="H34">
-        <v>2052</v>
       </c>
       <c r="I34">
         <f t="shared" si="3"/>
-        <v>1053267.37257196</v>
+        <v>977741.02886626148</v>
       </c>
       <c r="K34">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="L34">
         <f>I34*就业人口计算!E61</f>
-        <v>595587489778648</v>
+        <v>563518507382602.38</v>
       </c>
       <c r="N34">
+        <v>2051</v>
+      </c>
+      <c r="O34">
+        <f>L34*汇率!B53</f>
+        <v>39510158236278.445</v>
+      </c>
+    </row>
+    <row r="35" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H35">
         <v>2052</v>
-      </c>
-      <c r="O34">
-        <f>L34*汇率!B54</f>
-        <v>40859707763576.2</v>
-      </c>
-    </row>
-    <row r="35" spans="8:15">
-      <c r="H35">
-        <v>2053</v>
       </c>
       <c r="I35">
         <f t="shared" si="3"/>
-        <v>1134627.80569923</v>
+        <v>1053267.3725719557</v>
       </c>
       <c r="K35">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="L35">
         <f>I35*就业人口计算!E62</f>
-        <v>628508432333073</v>
+        <v>595587489778647.38</v>
       </c>
       <c r="N35">
+        <v>2052</v>
+      </c>
+      <c r="O35">
+        <f>L35*汇率!B54</f>
+        <v>40859707763576.211</v>
+      </c>
+    </row>
+    <row r="36" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H36">
         <v>2053</v>
-      </c>
-      <c r="O35">
-        <f>L35*汇率!B55</f>
-        <v>42190036606538.2</v>
-      </c>
-    </row>
-    <row r="36" spans="8:15">
-      <c r="H36">
-        <v>2054</v>
       </c>
       <c r="I36">
         <f t="shared" si="3"/>
-        <v>1222272.98688861</v>
+        <v>1134627.8056992271</v>
       </c>
       <c r="K36">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="L36">
         <f>I36*就业人口计算!E63</f>
-        <v>662474906135906</v>
+        <v>628508432333073</v>
       </c>
       <c r="N36">
+        <v>2053</v>
+      </c>
+      <c r="O36">
+        <f>L36*汇率!B55</f>
+        <v>42190036606538.18</v>
+      </c>
+    </row>
+    <row r="37" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H37">
         <v>2054</v>
-      </c>
-      <c r="O36">
-        <f>L36*汇率!B56</f>
-        <v>43512829997786.9</v>
-      </c>
-    </row>
-    <row r="37" spans="8:15">
-      <c r="H37">
-        <v>2055</v>
       </c>
       <c r="I37">
         <f t="shared" si="3"/>
-        <v>1316688.38624745</v>
+        <v>1222272.9868886105</v>
       </c>
       <c r="K37">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="L37">
         <f>I37*就业人口计算!E64</f>
-        <v>697951250028818</v>
+        <v>662474906135906.5</v>
       </c>
       <c r="N37">
+        <v>2054</v>
+      </c>
+      <c r="O37">
+        <f>L37*汇率!B56</f>
+        <v>43512829997786.938</v>
+      </c>
+    </row>
+    <row r="38" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H38">
         <v>2055</v>
-      </c>
-      <c r="O37">
-        <f>L37*汇率!B57</f>
-        <v>44856159904210.9</v>
-      </c>
-    </row>
-    <row r="38" spans="8:15">
-      <c r="H38">
-        <v>2056</v>
       </c>
       <c r="I38">
         <f t="shared" si="3"/>
-        <v>1418396.97438795</v>
+        <v>1316688.3862474542</v>
       </c>
       <c r="K38">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="L38">
         <f>I38*就业人口计算!E65</f>
-        <v>735807378610097</v>
+        <v>697951250028817.63</v>
       </c>
       <c r="N38">
+        <v>2055</v>
+      </c>
+      <c r="O38">
+        <f>L38*汇率!B57</f>
+        <v>44856159904210.891</v>
+      </c>
+    </row>
+    <row r="39" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H39">
         <v>2056</v>
-      </c>
-      <c r="O38">
-        <f>L38*汇率!B58</f>
-        <v>46271144809018.6</v>
-      </c>
-    </row>
-    <row r="39" spans="8:15">
-      <c r="H39">
-        <v>2057</v>
       </c>
       <c r="I39">
         <f t="shared" si="3"/>
-        <v>1527962.11918192</v>
+        <v>1418396.9743879479</v>
       </c>
       <c r="K39">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="L39">
         <f>I39*就业人口计算!E66</f>
-        <v>777496738184845</v>
+        <v>735807378610097.5</v>
       </c>
       <c r="N39">
+        <v>2056</v>
+      </c>
+      <c r="O39">
+        <f>L39*汇率!B58</f>
+        <v>46271144809018.586</v>
+      </c>
+    </row>
+    <row r="40" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H40">
         <v>2057</v>
-      </c>
-      <c r="O39">
-        <f>L39*汇率!B59</f>
-        <v>47840288058435.7</v>
-      </c>
-    </row>
-    <row r="40" spans="8:15">
-      <c r="H40">
-        <v>2058</v>
       </c>
       <c r="I40">
         <f t="shared" si="3"/>
-        <v>1645990.70627766</v>
+        <v>1527962.1191819219</v>
       </c>
       <c r="K40">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="L40">
         <f>I40*就业人口计算!E67</f>
-        <v>825287987115066</v>
+        <v>777496738184844.5</v>
       </c>
       <c r="N40">
+        <v>2057</v>
+      </c>
+      <c r="O40">
+        <f>L40*汇率!B59</f>
+        <v>47840288058435.672</v>
+      </c>
+    </row>
+    <row r="41" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H41">
         <v>2058</v>
-      </c>
-      <c r="O40">
-        <f>L40*汇率!B60</f>
-        <v>49687807996161.9</v>
-      </c>
-    </row>
-    <row r="41" spans="8:15">
-      <c r="H41">
-        <v>2059</v>
       </c>
       <c r="I41">
         <f t="shared" si="3"/>
-        <v>1773136.50066337</v>
+        <v>1645990.7062776566</v>
       </c>
       <c r="K41">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="L41">
         <f>I41*就业人口计算!E68</f>
-        <v>882563137041609</v>
+        <v>825287987115065.63</v>
       </c>
       <c r="N41">
+        <v>2058</v>
+      </c>
+      <c r="O41">
+        <f>L41*汇率!B60</f>
+        <v>49687807996161.93</v>
+      </c>
+    </row>
+    <row r="42" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H42">
         <v>2059</v>
-      </c>
-      <c r="O41">
-        <f>L41*汇率!B61</f>
-        <v>51992320667465.6</v>
-      </c>
-    </row>
-    <row r="42" spans="8:15">
-      <c r="H42">
-        <v>2060</v>
       </c>
       <c r="I42">
         <f t="shared" si="3"/>
-        <v>1910103.76789721</v>
+        <v>1773136.5006633692</v>
       </c>
       <c r="K42">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="L42">
         <f>I42*就业人口计算!E69</f>
-        <v>954197437584864</v>
+        <v>882563137041608.38</v>
       </c>
       <c r="N42">
+        <v>2059</v>
+      </c>
+      <c r="O42">
+        <f>L42*汇率!B61</f>
+        <v>51992320667465.617</v>
+      </c>
+    </row>
+    <row r="43" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H43">
         <v>2060</v>
       </c>
-      <c r="O42">
-        <f>L42*汇率!B62</f>
-        <v>55002289654939.8</v>
+      <c r="I43">
+        <f t="shared" si="3"/>
+        <v>1910103.7678972078</v>
+      </c>
+      <c r="K43">
+        <v>2060</v>
+      </c>
+      <c r="L43">
+        <f>I43*就业人口计算!E70</f>
+        <v>954197437584864.25</v>
+      </c>
+      <c r="N43">
+        <v>2060</v>
+      </c>
+      <c r="O43">
+        <f>L43*汇率!B62</f>
+        <v>55002289654939.828</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AP2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="43" width="18.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:42">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1">
+        <v>65</v>
+      </c>
+      <c r="B1" s="20">
+        <v>2019</v>
+      </c>
+      <c r="C1">
         <v>2020</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2021</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2022</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2023</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2024</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2025</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2026</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2027</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2028</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2029</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2030</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2031</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2032</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2033</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2034</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2035</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2036</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2037</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2038</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2039</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2040</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2041</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2042</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2043</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2044</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2045</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2046</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2047</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2048</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2049</v>
       </c>
-      <c r="AF1">
+      <c r="AG1">
         <v>2050</v>
       </c>
-      <c r="AG1">
+      <c r="AH1">
         <v>2051</v>
       </c>
-      <c r="AH1">
+      <c r="AI1">
         <v>2052</v>
       </c>
-      <c r="AI1">
+      <c r="AJ1">
         <v>2053</v>
       </c>
-      <c r="AJ1">
+      <c r="AK1">
         <v>2054</v>
       </c>
-      <c r="AK1">
+      <c r="AL1">
         <v>2055</v>
       </c>
-      <c r="AL1">
+      <c r="AM1">
         <v>2056</v>
       </c>
-      <c r="AM1">
+      <c r="AN1">
         <v>2057</v>
       </c>
-      <c r="AN1">
+      <c r="AO1">
         <v>2058</v>
       </c>
-      <c r="AO1">
+      <c r="AP1">
         <v>2059</v>
       </c>
-      <c r="AP1">
+      <c r="AQ1">
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:42">
-      <c r="A2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2">
+    <row r="2" spans="1:43" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="18">
+        <v>1404986233.33338</v>
+      </c>
+      <c r="C2" s="16">
         <v>1409794440</v>
       </c>
-      <c r="C2">
-        <v>1413833784.93008</v>
-      </c>
-      <c r="D2">
-        <v>1417114543.03414</v>
-      </c>
-      <c r="E2">
-        <v>1419656700.68877</v>
-      </c>
-      <c r="F2">
-        <v>1421488177.57082</v>
-      </c>
-      <c r="G2">
-        <v>1422643159.17969</v>
-      </c>
-      <c r="H2">
+      <c r="D2" s="16">
+        <v>1413833784.9300799</v>
+      </c>
+      <c r="E2" s="16">
+        <v>1417114543.0341401</v>
+      </c>
+      <c r="F2" s="16">
+        <v>1419656700.6887701</v>
+      </c>
+      <c r="G2" s="16">
+        <v>1421488177.5708201</v>
+      </c>
+      <c r="H2" s="16">
+        <v>1422643159.1796899</v>
+      </c>
+      <c r="I2" s="16">
         <v>1423160540.04778</v>
       </c>
-      <c r="I2">
-        <v>1423082477.63899</v>
-      </c>
-      <c r="J2">
+      <c r="J2" s="16">
+        <v>1423082477.6389899</v>
+      </c>
+      <c r="K2" s="16">
         <v>1422453056.93542</v>
       </c>
-      <c r="K2">
-        <v>1421317065.71212</v>
-      </c>
-      <c r="L2">
+      <c r="L2" s="16">
+        <v>1421317065.7121201</v>
+      </c>
+      <c r="M2" s="16">
         <v>1419718880.5</v>
       </c>
-      <c r="M2">
+      <c r="N2" s="16">
         <v>1417701463.23684</v>
       </c>
-      <c r="N2">
-        <v>1415305468.60646</v>
-      </c>
-      <c r="O2">
-        <v>1412568462.06595</v>
-      </c>
-      <c r="P2">
+      <c r="O2" s="16">
+        <v>1415305468.6064601</v>
+      </c>
+      <c r="P2" s="16">
+        <v>1412568462.0659499</v>
+      </c>
+      <c r="Q2" s="16">
         <v>1409524248.56106</v>
       </c>
-      <c r="Q2">
-        <v>1406202311.92969</v>
-      </c>
-      <c r="R2">
+      <c r="R2" s="16">
+        <v>1406202311.9296899</v>
+      </c>
+      <c r="S2" s="16">
         <v>1402627364.99354</v>
       </c>
-      <c r="S2">
+      <c r="T2" s="16">
         <v>1398819010.33781</v>
       </c>
-      <c r="T2">
-        <v>1394791511.7791</v>
-      </c>
-      <c r="U2">
-        <v>1390553676.52136</v>
-      </c>
-      <c r="V2">
+      <c r="U2" s="16">
+        <v>1394791511.7790999</v>
+      </c>
+      <c r="V2" s="16">
+        <v>1390553676.5213599</v>
+      </c>
+      <c r="W2" s="16">
         <v>1386108848</v>
       </c>
-      <c r="W2">
-        <v>1381455009.4141</v>
-      </c>
-      <c r="X2">
+      <c r="X2" s="16">
+        <v>1381455009.4140999</v>
+      </c>
+      <c r="Y2" s="16">
         <v>1376584997.94678</v>
       </c>
-      <c r="Y2">
+      <c r="Z2" s="16">
         <v>1371486829.67363</v>
       </c>
-      <c r="Z2">
-        <v>1366144135.15929</v>
-      </c>
-      <c r="AA2">
-        <v>1360536705.74219</v>
-      </c>
-      <c r="AB2">
-        <v>1354641150.5073</v>
-      </c>
-      <c r="AC2">
+      <c r="AA2" s="16">
+        <v>1366144135.1592901</v>
+      </c>
+      <c r="AB2" s="16">
+        <v>1360536705.7421899</v>
+      </c>
+      <c r="AC2" s="16">
+        <v>1354641150.5072999</v>
+      </c>
+      <c r="AD2" s="16">
         <v>1348431663.94713</v>
       </c>
-      <c r="AD2">
+      <c r="AE2" s="16">
         <v>1341880904.31078</v>
       </c>
-      <c r="AE2">
-        <v>1334960982.6411</v>
-      </c>
-      <c r="AF2">
+      <c r="AF2" s="16">
+        <v>1334960982.6410999</v>
+      </c>
+      <c r="AG2" s="16">
         <v>1327644562.5</v>
       </c>
-      <c r="AG2">
+      <c r="AH2" s="16">
         <v>1319906070.38186</v>
       </c>
-      <c r="AH2">
+      <c r="AI2" s="16">
         <v>1311723016.8151</v>
       </c>
-      <c r="AI2">
-        <v>1303077428.15181</v>
-      </c>
-      <c r="AJ2">
-        <v>1293957389.04554</v>
-      </c>
-      <c r="AK2">
-        <v>1284358695.61718</v>
-      </c>
-      <c r="AL2">
-        <v>1274286619.30905</v>
-      </c>
-      <c r="AM2">
+      <c r="AJ2" s="16">
+        <v>1303077428.1518099</v>
+      </c>
+      <c r="AK2" s="16">
+        <v>1293957389.0455401</v>
+      </c>
+      <c r="AL2" s="16">
+        <v>1284358695.6171801</v>
+      </c>
+      <c r="AM2" s="16">
+        <v>1274286619.3090501</v>
+      </c>
+      <c r="AN2" s="16">
         <v>1263757781.42695</v>
       </c>
-      <c r="AN2">
+      <c r="AO2" s="16">
         <v>1252802138.37046</v>
       </c>
-      <c r="AO2">
-        <v>1241465077.55134</v>
-      </c>
-      <c r="AP2">
+      <c r="AP2" s="16">
+        <v>1241465077.5513401</v>
+      </c>
+      <c r="AQ2" s="16">
         <v>1229809624</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AP2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:42">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1">
+        <v>65</v>
+      </c>
+      <c r="B1" s="20">
+        <v>2019</v>
+      </c>
+      <c r="C1">
         <v>2020</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2021</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2022</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2023</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2024</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2025</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2026</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2027</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2028</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2029</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2030</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2031</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2032</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2033</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2034</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2035</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2036</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2037</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2038</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2039</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2040</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2041</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2042</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2043</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2044</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2045</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2046</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2047</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2048</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2049</v>
       </c>
-      <c r="AF1">
+      <c r="AG1">
         <v>2050</v>
       </c>
-      <c r="AG1">
+      <c r="AH1">
         <v>2051</v>
       </c>
-      <c r="AH1">
+      <c r="AI1">
         <v>2052</v>
       </c>
-      <c r="AI1">
+      <c r="AJ1">
         <v>2053</v>
       </c>
-      <c r="AJ1">
+      <c r="AK1">
         <v>2054</v>
       </c>
-      <c r="AK1">
+      <c r="AL1">
         <v>2055</v>
       </c>
-      <c r="AL1">
+      <c r="AM1">
         <v>2056</v>
       </c>
-      <c r="AM1">
+      <c r="AN1">
         <v>2057</v>
       </c>
-      <c r="AN1">
+      <c r="AO1">
         <v>2058</v>
       </c>
-      <c r="AO1">
+      <c r="AP1">
         <v>2059</v>
       </c>
-      <c r="AP1">
+      <c r="AQ1">
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:42">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2">
+        <v>67</v>
+      </c>
+      <c r="B2" s="7">
+        <v>756075416.75402272</v>
+      </c>
+      <c r="C2">
         <v>750640000</v>
       </c>
-      <c r="C2">
-        <v>748756491.720689</v>
-      </c>
       <c r="D2">
-        <v>749009036.114951</v>
+        <v>748756491.72068906</v>
       </c>
       <c r="E2">
-        <v>750280905.802214</v>
+        <v>749009036.11495101</v>
       </c>
       <c r="F2">
-        <v>751717864.672639</v>
+        <v>750280905.80221403</v>
       </c>
       <c r="G2">
-        <v>752693601.256759</v>
+        <v>751717864.67263901</v>
       </c>
       <c r="H2">
+        <v>752693601.25675905</v>
+      </c>
+      <c r="I2">
         <v>752777232.614622</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>751702878.744326</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>749341307.510095</v>
       </c>
-      <c r="K2">
-        <v>745673650.089779</v>
-      </c>
       <c r="L2">
-        <v>740767186.941829</v>
+        <v>745673650.08977902</v>
       </c>
       <c r="M2">
-        <v>734753204.291751</v>
+        <v>740767186.94182897</v>
       </c>
       <c r="N2">
-        <v>727806921.137978</v>
+        <v>734753204.29175103</v>
       </c>
       <c r="O2">
-        <v>720129486.777337</v>
+        <v>727806921.13797796</v>
       </c>
       <c r="P2">
-        <v>711932048.849788</v>
+        <v>720129486.77733696</v>
       </c>
       <c r="Q2">
-        <v>703421891.90281</v>
+        <v>711932048.84978795</v>
       </c>
       <c r="R2">
-        <v>694790646.475145</v>
+        <v>703421891.90280998</v>
       </c>
       <c r="S2">
-        <v>686204568.700009</v>
+        <v>694790646.47514498</v>
       </c>
       <c r="T2">
-        <v>677796890.427915</v>
+        <v>686204568.70000899</v>
       </c>
       <c r="U2">
+        <v>677796890.42791498</v>
+      </c>
+      <c r="V2">
         <v>669662239.868734</v>
       </c>
-      <c r="V2">
-        <v>661853132.753382</v>
-      </c>
       <c r="W2">
-        <v>654378534.014948</v>
+        <v>661853132.75338197</v>
       </c>
       <c r="X2">
-        <v>647204489.989217</v>
+        <v>654378534.01494801</v>
       </c>
       <c r="Y2">
-        <v>640256831.134797</v>
+        <v>647204489.98921704</v>
       </c>
       <c r="Z2">
-        <v>633425945.272573</v>
+        <v>640256831.13479698</v>
       </c>
       <c r="AA2">
-        <v>626573621.344687</v>
+        <v>633425945.27257299</v>
       </c>
       <c r="AB2">
-        <v>619541963.692974</v>
+        <v>626573621.34468699</v>
       </c>
       <c r="AC2">
-        <v>612164376.856912</v>
+        <v>619541963.69297397</v>
       </c>
       <c r="AD2">
-        <v>604278620.890984</v>
+        <v>612164376.85691202</v>
       </c>
       <c r="AE2">
-        <v>595741937.201462</v>
+        <v>604278620.89098406</v>
       </c>
       <c r="AF2">
-        <v>586448244.902788</v>
+        <v>595741937.20146203</v>
       </c>
       <c r="AG2">
-        <v>576347407.693456</v>
+        <v>586448244.90278804</v>
       </c>
       <c r="AH2">
-        <v>565466571.250843</v>
+        <v>576347407.69345605</v>
       </c>
       <c r="AI2">
-        <v>553933571.146485</v>
+        <v>565466571.25084305</v>
       </c>
       <c r="AJ2">
-        <v>542002411.279895</v>
+        <v>553933571.14648497</v>
       </c>
       <c r="AK2">
-        <v>530080812.832238</v>
+        <v>542002411.27989495</v>
       </c>
       <c r="AL2">
-        <v>518759833.739497</v>
+        <v>530080812.83223802</v>
       </c>
       <c r="AM2">
-        <v>508845558.685133</v>
+        <v>518759833.73949701</v>
       </c>
       <c r="AN2">
-        <v>501392859.61184</v>
+        <v>508845558.68513298</v>
       </c>
       <c r="AO2">
-        <v>497741226.753509</v>
+        <v>501392859.61184001</v>
       </c>
       <c r="AP2">
-        <v>499552670.185725</v>
+        <v>497741226.75350899</v>
+      </c>
+      <c r="AQ2">
+        <v>499552670.18572497</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AP2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:42">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B1">
+        <v>2019</v>
+      </c>
+      <c r="C1">
         <v>2020</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2021</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2022</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2023</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2024</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2025</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2026</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2027</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2028</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2029</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2030</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2031</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2032</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2033</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2034</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2035</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2036</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2037</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2038</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2039</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2040</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2041</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2042</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2043</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2044</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2045</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2046</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2047</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2048</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2049</v>
       </c>
-      <c r="AF1">
+      <c r="AG1">
         <v>2050</v>
       </c>
-      <c r="AG1">
+      <c r="AH1">
         <v>2051</v>
       </c>
-      <c r="AH1">
+      <c r="AI1">
         <v>2052</v>
       </c>
-      <c r="AI1">
+      <c r="AJ1">
         <v>2053</v>
       </c>
-      <c r="AJ1">
+      <c r="AK1">
         <v>2054</v>
       </c>
-      <c r="AK1">
+      <c r="AL1">
         <v>2055</v>
       </c>
-      <c r="AL1">
+      <c r="AM1">
         <v>2056</v>
       </c>
-      <c r="AM1">
+      <c r="AN1">
         <v>2057</v>
       </c>
-      <c r="AN1">
+      <c r="AO1">
         <v>2058</v>
       </c>
-      <c r="AO1">
+      <c r="AP1">
         <v>2059</v>
       </c>
-      <c r="AP1">
+      <c r="AQ1">
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:42">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2">
+        <v>69</v>
+      </c>
+      <c r="B2" s="6">
+        <v>9477713619655.707</v>
+      </c>
+      <c r="C2">
         <v>10061792771500.1</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>10579086336261.6</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>11154715888934</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>11777666314251.5</v>
       </c>
-      <c r="F2">
-        <v>12438102130933.8</v>
-      </c>
       <c r="G2">
+        <v>12438102130933.801</v>
+      </c>
+      <c r="H2">
         <v>13127480040440.1</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>13838643248878.4</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>14565894060916.9</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>15305041191632.9</v>
       </c>
-      <c r="K2">
-        <v>16053418263175.7</v>
-      </c>
       <c r="L2">
-        <v>16809870066079.2</v>
+        <v>16053418263175.699</v>
       </c>
       <c r="M2">
+        <v>16809870066079.199</v>
+      </c>
+      <c r="N2">
         <v>17574703391078</v>
       </c>
-      <c r="N2">
-        <v>18349599600685.8</v>
-      </c>
       <c r="O2">
-        <v>19137486638604.6</v>
+        <v>18349599600685.801</v>
       </c>
       <c r="P2">
-        <v>19942368901402.2</v>
+        <v>19137486638604.602</v>
       </c>
       <c r="Q2">
+        <v>19942368901402.199</v>
+      </c>
+      <c r="R2">
         <v>20769114357701.5</v>
       </c>
-      <c r="R2">
-        <v>21623199537405.6</v>
-      </c>
       <c r="S2">
-        <v>22510414575272.3</v>
+        <v>21623199537405.602</v>
       </c>
       <c r="T2">
-        <v>23436532433989.2</v>
+        <v>22510414575272.301</v>
       </c>
       <c r="U2">
+        <v>23436532433989.199</v>
+      </c>
+      <c r="V2">
         <v>24406948813717.5</v>
       </c>
-      <c r="V2">
-        <v>25426302148134.8</v>
-      </c>
       <c r="W2">
-        <v>26498086570621.1</v>
+        <v>25426302148134.801</v>
       </c>
       <c r="X2">
-        <v>27624274898147.9</v>
+        <v>26498086570621.102</v>
       </c>
       <c r="Y2">
-        <v>28804973625731.7</v>
+        <v>27624274898147.898</v>
       </c>
       <c r="Z2">
-        <v>30038137764849.7</v>
+        <v>28804973625731.699</v>
       </c>
       <c r="AA2">
-        <v>31319380223052.7</v>
+        <v>30038137764849.699</v>
       </c>
       <c r="AB2">
-        <v>32641918452907.7</v>
+        <v>31319380223052.699</v>
       </c>
       <c r="AC2">
-        <v>33996710457655.9</v>
+        <v>32641918452907.699</v>
       </c>
       <c r="AD2">
-        <v>35372843109278.8</v>
+        <v>33996710457655.898</v>
       </c>
       <c r="AE2">
-        <v>36758248314259.7</v>
+        <v>35372843109278.797</v>
       </c>
       <c r="AF2">
-        <v>38140837079322.8</v>
+        <v>36758248314259.703</v>
       </c>
       <c r="AG2">
-        <v>39510158236278.4</v>
+        <v>38140837079322.797</v>
       </c>
       <c r="AH2">
-        <v>40859707763576.2</v>
+        <v>39510158236278.398</v>
       </c>
       <c r="AI2">
-        <v>42190036606538.2</v>
+        <v>40859707763576.203</v>
       </c>
       <c r="AJ2">
-        <v>43512829997786.9</v>
+        <v>42190036606538.203</v>
       </c>
       <c r="AK2">
-        <v>44856159904210.9</v>
+        <v>43512829997786.898</v>
       </c>
       <c r="AL2">
-        <v>46271144809018.6</v>
+        <v>44856159904210.898</v>
       </c>
       <c r="AM2">
-        <v>47840288058435.7</v>
+        <v>46271144809018.602</v>
       </c>
       <c r="AN2">
-        <v>49687807996161.9</v>
+        <v>47840288058435.703</v>
       </c>
       <c r="AO2">
-        <v>51992320667465.6</v>
+        <v>49687807996161.898</v>
       </c>
       <c r="AP2">
-        <v>55002289654939.8</v>
+        <v>51992320667465.602</v>
+      </c>
+      <c r="AQ2">
+        <v>55002289654939.797</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" ht="42.75" spans="1:2">
+    <row r="1" spans="1:2" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" s="4">
         <f>[1]Calculation!L45</f>
-        <v>0.264027318393146</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>0.26402731839314603</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B3" s="4">
         <f>[1]Calculation!L46</f>
-        <v>0.258730967526493</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>0.25873096752649299</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B4" s="4">
         <f>[1]Calculation!L47</f>
-        <v>0.257182474220425</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>0.25718247422042501</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B5" s="4">
         <f>[1]Calculation!L48</f>
-        <v>0.250657416210714</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>0.25065741621071402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B6" s="4">
         <f>[1]Calculation!L49</f>
         <v>0.234364418959083</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B7" s="4">
         <f>[1]Calculation!L50</f>
-        <v>0.225559165944784</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>0.22555916594478401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B8" s="4">
         <f>[1]Calculation!L51</f>
         <v>0.217037097117422</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B9" s="4">
         <f>[1]Calculation!L52</f>
-        <v>0.201427126315792</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>0.20142712631579199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B10" s="4">
         <f>[1]Calculation!L53</f>
         <v>0.186860689001348</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B11" s="4">
         <f>[1]Calculation!L54</f>
         <v>0.187253046603439</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B12" s="4">
         <f>[1]Calculation!L55</f>
-        <v>0.175197070022782</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>0.17519707002278201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B13" s="4">
         <f>[1]Calculation!L56</f>
-        <v>0.162105908361236</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>0.16210590836123601</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B14" s="4">
         <f>[1]Calculation!L57</f>
         <v>0.158412957650193</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B15" s="4">
         <f>[1]Calculation!L58</f>
-        <v>0.155058469203377</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>0.15505846920337699</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B16" s="4">
         <f>[1]Calculation!L59</f>
-        <v>0.153476033552131</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>0.15347603355213099</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B17" s="4">
         <f>[1]Calculation!L60</f>
         <v>0.153480552163204</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B18" s="4">
         <f>[1]Calculation!L61</f>
-        <v>0.151350526540712</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>0.15135052654071199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B19" s="4">
         <f>[1]Calculation!L62</f>
-        <v>0.145204482579299</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>0.14520448257929899</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B20" s="4">
         <f>[1]Calculation!L63</f>
-        <v>0.140294528147456</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>0.14029452814745599</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B21" s="4">
         <f>[1]Calculation!L64</f>
         <v>0.138511262027254</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B22" s="4">
         <f>[1]Calculation!L65</f>
-        <v>0.137650677988234</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>0.13765067798823399</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>2021</v>
       </c>
       <c r="B23">
         <f t="shared" ref="B23:B62" si="0">B22/(1+0.022)</f>
-        <v>0.134687551847587</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>0.13468755184758707</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>2022</v>
       </c>
       <c r="B24">
         <f t="shared" si="0"/>
-        <v>0.131788211201162</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>0.13178821120116152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>2023</v>
       </c>
       <c r="B25">
         <f t="shared" si="0"/>
-        <v>0.128951282975696</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>0.12895128297569619</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>2024</v>
       </c>
       <c r="B26">
         <f t="shared" si="0"/>
-        <v>0.12617542365528</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>0.12617542365528003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>2025</v>
       </c>
       <c r="B27">
         <f t="shared" si="0"/>
-        <v>0.123459318645088</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>0.12345931864508809</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>2026</v>
       </c>
       <c r="B28">
         <f t="shared" si="0"/>
-        <v>0.120801681648814</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>0.12080168164881418</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>2027</v>
       </c>
       <c r="B29">
         <f t="shared" si="0"/>
-        <v>0.118201254059505</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>0.11820125405950506</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>2028</v>
       </c>
       <c r="B30">
         <f t="shared" si="0"/>
-        <v>0.115656804363508</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>0.11565680436350788</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>2029</v>
       </c>
       <c r="B31">
         <f t="shared" si="0"/>
-        <v>0.113167127557248</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>0.11316712755724841</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2030</v>
       </c>
       <c r="B32">
         <f t="shared" si="0"/>
-        <v>0.110731044576564</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>0.11073104457656399</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2031</v>
       </c>
       <c r="B33">
         <f t="shared" si="0"/>
-        <v>0.108347401738321</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>0.10834740173832093</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2032</v>
       </c>
       <c r="B34">
         <f t="shared" si="0"/>
-        <v>0.106015070194052</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>0.10601507019405179</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>2033</v>
       </c>
       <c r="B35">
         <f t="shared" si="0"/>
-        <v>0.103732945395354</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>0.10373294539535401</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2034</v>
       </c>
       <c r="B36">
         <f t="shared" si="0"/>
-        <v>0.101499946570796</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>0.10149994657079649</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2035</v>
       </c>
       <c r="B37">
         <f t="shared" si="0"/>
-        <v>0.0993150162140866</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>9.9315016214086574E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2036</v>
       </c>
       <c r="B38">
         <f t="shared" si="0"/>
-        <v>0.097177119583255</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>9.7177119583254964E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>2037</v>
       </c>
       <c r="B39">
         <f t="shared" si="0"/>
-        <v>0.0950852442106213</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>9.5085244210621298E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2038</v>
       </c>
       <c r="B40">
         <f t="shared" si="0"/>
-        <v>0.0930383994233085</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>9.3038399423308507E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2039</v>
       </c>
       <c r="B41">
         <f t="shared" si="0"/>
-        <v>0.0910356158740788</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>9.1035615874078768E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2040</v>
       </c>
       <c r="B42">
         <f t="shared" si="0"/>
-        <v>0.0890759450822688</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>8.9075945082268848E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>2041</v>
       </c>
       <c r="B43">
         <f t="shared" si="0"/>
-        <v>0.0871584589846075</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>8.7158458984607487E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2042</v>
       </c>
       <c r="B44">
         <f t="shared" si="0"/>
-        <v>0.085282249495702</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>8.5282249495702039E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2043</v>
       </c>
       <c r="B45">
         <f t="shared" si="0"/>
-        <v>0.0834464280779863</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>8.3446428077986343E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2044</v>
       </c>
       <c r="B46">
         <f t="shared" si="0"/>
-        <v>0.081650125320926</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>8.165012532092597E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2045</v>
       </c>
       <c r="B47">
         <f t="shared" si="0"/>
-        <v>0.0798924905292818</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>7.9892490529281768E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2046</v>
       </c>
       <c r="B48">
         <f t="shared" si="0"/>
-        <v>0.0781726913202366</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>7.8172691320236562E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2047</v>
       </c>
       <c r="B49">
         <f t="shared" si="0"/>
-        <v>0.0764899132291943</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>7.6489913229194281E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2048</v>
       </c>
       <c r="B50">
         <f t="shared" si="0"/>
-        <v>0.0748433593240649</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>7.4843359324064856E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2049</v>
       </c>
       <c r="B51">
         <f t="shared" si="0"/>
-        <v>0.0732322498278521</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>7.3232249827852106E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2050</v>
       </c>
       <c r="B52">
         <f t="shared" si="0"/>
-        <v>0.071655821749366</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>7.165582174936605E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2051</v>
       </c>
       <c r="B53">
         <f t="shared" si="0"/>
-        <v>0.0701133285218846</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>7.0113328521884594E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>2052</v>
       </c>
       <c r="B54">
         <f t="shared" si="0"/>
-        <v>0.0686040396495935</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>6.8604039649593537E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>2053</v>
       </c>
       <c r="B55">
         <f t="shared" si="0"/>
-        <v>0.0671272403616375</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>6.7127240361637516E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>2054</v>
       </c>
       <c r="B56">
         <f t="shared" si="0"/>
-        <v>0.0656822312736179</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>6.5682231273617928E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>2055</v>
       </c>
       <c r="B57">
         <f t="shared" si="0"/>
-        <v>0.0642683280563776</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>6.4268328056377624E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>2056</v>
       </c>
       <c r="B58">
         <f t="shared" si="0"/>
-        <v>0.0628848611119155</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>6.2884861111915477E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>2057</v>
       </c>
       <c r="B59">
         <f t="shared" si="0"/>
-        <v>0.0615311752562774</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>6.1531175256277375E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>2058</v>
       </c>
       <c r="B60">
         <f t="shared" si="0"/>
-        <v>0.0602066294092734</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>6.0206629409273363E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>2059</v>
       </c>
       <c r="B61">
         <f t="shared" si="0"/>
-        <v>0.0589105962908741</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>5.8910596290874133E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>2060</v>
       </c>
       <c r="B62">
         <f t="shared" si="0"/>
-        <v>0.057642462124143</v>
+        <v>5.7642462124142986E-2</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/InputData/io-model/BPEaCP/cn-BAU Pop Employment and Compensation Projections.xlsx
+++ b/InputData/io-model/BPEaCP/cn-BAU Pop Employment and Compensation Projections.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlx6\Desktop\eps-china2019-smart-trans\InputData\io-model\BPEaCP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AAA425-5D60-40F0-B97A-C27E7DED3684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBD09C3-6883-48A2-B4B4-A1D5881F8289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28665" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="6" r:id="rId1"/>
@@ -41,8 +41,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="103">
   <si>
     <t>BPEaCP BAU Population Employment and Compensation Projections</t>
   </si>
@@ -336,6 +358,30 @@
   </si>
   <si>
     <t>2019年就业比重</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020年就业比重</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021年就业比重</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022年就业比重</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2023年就业比重</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024年就业比重</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025年就业比重</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -345,9 +391,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="0.0000_ "/>
+    <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -420,6 +466,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -438,7 +492,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -449,21 +503,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -499,8 +556,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
+    <cellStyle name="百分比" xfId="4" builtinId="5"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="超链接" xfId="2" builtinId="8"/>
@@ -2995,19 +3062,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="12"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
@@ -3015,82 +3082,82 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>2021</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>2020</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B18" s="14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -3108,16 +3175,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S75"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S81"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" customWidth="1"/>
-    <col min="2" max="6" width="9.6640625" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" customWidth="1"/>
-    <col min="8" max="19" width="9.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.875" customWidth="1"/>
+    <col min="2" max="6" width="9.625" customWidth="1"/>
+    <col min="7" max="7" width="10.125" customWidth="1"/>
+    <col min="8" max="19" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>15</v>
       </c>
@@ -3173,7 +3240,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -3232,7 +3299,7 @@
         <v>20494609.353016399</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -3291,7 +3358,7 @@
         <v>23899642.002179701</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -3350,7 +3417,7 @@
         <v>26434347.5475915</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -3409,7 +3476,7 @@
         <v>26357174.000212502</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -3468,7 +3535,7 @@
         <v>24763066.909888301</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -3527,7 +3594,7 @@
         <v>24227283.691434901</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -3586,7 +3653,7 @@
         <v>25174311.976272799</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -3645,7 +3712,7 @@
         <v>29759089.5024211</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -3704,7 +3771,7 @@
         <v>40124662.391677</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -3763,7 +3830,7 @@
         <v>46834154.509930298</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -3822,7 +3889,7 @@
         <v>43997936.424949199</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -3881,7 +3948,7 @@
         <v>37008745.942879803</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -3940,7 +4007,7 @@
         <v>36553014.219432503</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -3999,7 +4066,7 @@
         <v>42304200.528976701</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -4058,7 +4125,7 @@
         <v>52135620.9728387</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -4117,7 +4184,7 @@
         <v>36846503.1713273</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -4176,7 +4243,7 @@
         <v>28290274.469443399</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -4235,7 +4302,7 @@
         <v>24070523.0161714</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -4294,7 +4361,7 @@
         <v>13117641.963315999</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -4353,7 +4420,7 @@
         <v>3497490.7906592102</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -4412,7 +4479,7 @@
         <v>387967.68335893902</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>20</v>
       </c>
@@ -4462,7 +4529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -4524,7 +4591,7 @@
         <v>1299652000</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -4586,7 +4653,7 @@
         <v>9157020000</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
         <v>56</v>
       </c>
@@ -4603,7 +4670,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="17">
         <v>2019</v>
       </c>
@@ -4619,12 +4686,12 @@
         <f>$L$26*B29^6+$M$26*B29^5+$N$26*B29^4+$O$26*B29^3+$P$26*B29^2+$Q$26*B29+$R$26</f>
         <v>972809418.79524612</v>
       </c>
-      <c r="E29">
-        <f>D29*$B$75</f>
+      <c r="E29" s="24">
+        <f>D29*B75</f>
         <v>756075416.75402272</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>2020</v>
       </c>
@@ -4640,855 +4707,855 @@
         <f>$L$26*B30^6+$M$26*B30^5+$N$26*B30^4+$O$26*B30^3+$P$26*B30^2+$Q$26*B30+$R$26</f>
         <v>965815904</v>
       </c>
-      <c r="E30">
-        <f>D30*$B$75</f>
-        <v>750639999.99999964</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E30" s="24">
+        <f t="shared" ref="E30:E35" si="2">D30*B76</f>
+        <v>749086815.14239991</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2021</v>
       </c>
       <c r="B31">
-        <f t="shared" ref="B31:B70" si="2">A31-2000</f>
+        <f t="shared" ref="B31:B70" si="3">A31-2000</f>
         <v>21</v>
       </c>
       <c r="C31" s="10">
-        <f t="shared" ref="C31:C70" si="3">$L$25*B31^6+$M$25*B31^5+$N$25*B31^4+$O$25*B31^3+$P$25*B31^2+$Q$25*B31+$R$25</f>
+        <f t="shared" ref="C31:C70" si="4">$L$25*B31^6+$M$25*B31^5+$N$25*B31^4+$O$25*B31^3+$P$25*B31^2+$Q$25*B31+$R$25</f>
         <v>1413833784.9300835</v>
       </c>
       <c r="D31" s="10">
-        <f t="shared" ref="D31:D70" si="4">$L$26*B31^6+$M$26*B31^5+$N$26*B31^4+$O$26*B31^3+$P$26*B31^2+$Q$26*B31+$R$26</f>
+        <f t="shared" ref="D31:D70" si="5">$L$26*B31^6+$M$26*B31^5+$N$26*B31^4+$O$26*B31^3+$P$26*B31^2+$Q$26*B31+$R$26</f>
         <v>963392475.65688705</v>
       </c>
-      <c r="E31">
-        <f t="shared" ref="E31:E70" si="5">D31*$B$75</f>
-        <v>748756491.72068858</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E31" s="24">
+        <f t="shared" si="2"/>
+        <v>745087740.67303646</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>2022</v>
       </c>
       <c r="B32">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="C32" s="10">
+        <f t="shared" si="4"/>
+        <v>1417114543.0341439</v>
+      </c>
+      <c r="D32" s="10">
+        <f t="shared" si="5"/>
+        <v>963717413.56646347</v>
+      </c>
+      <c r="E32" s="24">
         <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="C32" s="10">
-        <f t="shared" si="3"/>
-        <v>1417114543.0341439</v>
-      </c>
-      <c r="D32" s="10">
-        <f t="shared" si="4"/>
-        <v>963717413.56646347</v>
-      </c>
-      <c r="E32">
-        <f t="shared" si="5"/>
-        <v>749009036.11495066</v>
+        <v>734545412.62035847</v>
       </c>
       <c r="G32" s="18" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2023</v>
       </c>
       <c r="B33">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="C33" s="10">
+        <f t="shared" si="4"/>
+        <v>1419656700.6887715</v>
+      </c>
+      <c r="D33" s="10">
+        <f t="shared" si="5"/>
+        <v>965353873.08337402</v>
+      </c>
+      <c r="E33" s="24">
         <f t="shared" si="2"/>
-        <v>23</v>
-      </c>
-      <c r="C33" s="10">
-        <f t="shared" si="3"/>
-        <v>1419656700.6887715</v>
-      </c>
-      <c r="D33" s="10">
-        <f t="shared" si="4"/>
-        <v>965353873.08337402</v>
-      </c>
-      <c r="E33">
-        <f t="shared" si="5"/>
-        <v>750280905.80221331</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>745060119.24574816</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>2024</v>
       </c>
       <c r="B34">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="C34" s="10">
+        <f t="shared" si="4"/>
+        <v>1421488177.570816</v>
+      </c>
+      <c r="D34" s="10">
+        <f t="shared" si="5"/>
+        <v>967202745.6860199</v>
+      </c>
+      <c r="E34" s="24">
         <f t="shared" si="2"/>
-        <v>24</v>
-      </c>
-      <c r="C34" s="10">
-        <f t="shared" si="3"/>
-        <v>1421488177.570816</v>
-      </c>
-      <c r="D34" s="10">
-        <f t="shared" si="4"/>
-        <v>967202745.6860199</v>
-      </c>
-      <c r="E34">
-        <f t="shared" si="5"/>
-        <v>751717864.67263806</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>735557688.09421813</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2025</v>
       </c>
       <c r="B35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="C35" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1422643159.1796875</v>
       </c>
       <c r="D35" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>968458183.59375</v>
       </c>
-      <c r="E35">
-        <f t="shared" si="5"/>
-        <v>752693601.25675893</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E35" s="24">
+        <f>D35*$B$81</f>
+        <v>729926932.97460938</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2026</v>
       </c>
       <c r="B36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="C36" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1423160540.0477757</v>
       </c>
       <c r="D36" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>968565788.43161774</v>
       </c>
-      <c r="E36">
-        <f t="shared" si="5"/>
-        <v>752777232.61462176</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E36" s="24">
+        <f t="shared" ref="E36:E69" si="6">D36*$B$81</f>
+        <v>730008034.74091029</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>2027</v>
       </c>
       <c r="B37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="C37" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1423082477.6389916</v>
       </c>
       <c r="D37" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>967183463.94257355</v>
       </c>
-      <c r="E37">
-        <f t="shared" si="5"/>
-        <v>751702878.7443254</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E37" s="24">
+        <f t="shared" si="6"/>
+        <v>728966176.77351773</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>2028</v>
       </c>
       <c r="B38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="C38" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1422453056.9354239</v>
       </c>
       <c r="D38" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>964144932.74726105</v>
       </c>
-      <c r="E38">
-        <f t="shared" si="5"/>
-        <v>749341307.51009429</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E38" s="24">
+        <f t="shared" si="6"/>
+        <v>726676035.8116107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>2029</v>
       </c>
       <c r="B39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="C39" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1421317065.7121234</v>
       </c>
       <c r="D39" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>959425917.15128326</v>
       </c>
-      <c r="E39">
-        <f t="shared" si="5"/>
-        <v>745673650.0897783</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E39" s="24">
+        <f t="shared" si="6"/>
+        <v>723119313.75692225</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>2030</v>
       </c>
       <c r="B40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="C40" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1419718880.5</v>
       </c>
       <c r="D40" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>953112984</v>
       </c>
-      <c r="E40">
-        <f t="shared" si="5"/>
-        <v>740767186.94182909</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E40" s="24">
+        <f t="shared" si="6"/>
+        <v>718361256.04079998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>2031</v>
       </c>
       <c r="B41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="C41" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1417701463.2368436</v>
       </c>
       <c r="D41" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>945375053.58085632</v>
       </c>
-      <c r="E41">
-        <f t="shared" si="5"/>
-        <v>734753204.29175043</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E41" s="24">
+        <f t="shared" si="6"/>
+        <v>712529177.88389146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>2032</v>
       </c>
       <c r="B42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="C42" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1415305468.6064639</v>
       </c>
       <c r="D42" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>936437572.57318115</v>
       </c>
-      <c r="E42">
-        <f t="shared" si="5"/>
-        <v>727806921.13797736</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E42" s="24">
+        <f t="shared" si="6"/>
+        <v>705792998.4484067</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>2033</v>
       </c>
       <c r="B43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>33</v>
       </c>
       <c r="C43" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1412568462.0659509</v>
       </c>
       <c r="D43" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>926559351.0456543</v>
       </c>
-      <c r="E43">
-        <f t="shared" si="5"/>
-        <v>720129486.77733684</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E43" s="24">
+        <f t="shared" si="6"/>
+        <v>698347782.88310969</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>2034</v>
       </c>
       <c r="B44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="C44" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1409524248.5610561</v>
       </c>
       <c r="D44" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>916012063.50105286</v>
       </c>
-      <c r="E44">
-        <f t="shared" si="5"/>
-        <v>711932048.84978783</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E44" s="24">
+        <f t="shared" si="6"/>
+        <v>690398292.26074362</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>2035</v>
       </c>
       <c r="B45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
       <c r="C45" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1406202311.9296875</v>
       </c>
       <c r="D45" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>905062413.96875</v>
       </c>
-      <c r="E45">
-        <f t="shared" si="5"/>
-        <v>703421891.90280938</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E45" s="24">
+        <f t="shared" si="6"/>
+        <v>682145541.40824687</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>2036</v>
       </c>
       <c r="B46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>36</v>
       </c>
       <c r="C46" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1402627364.993536</v>
       </c>
       <c r="D46" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>893956965.14459229</v>
       </c>
-      <c r="E46">
-        <f t="shared" si="5"/>
-        <v>694790646.47514486</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E46" s="24">
+        <f t="shared" si="6"/>
+        <v>673775364.62947929</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>2037</v>
       </c>
       <c r="B47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="C47" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1398819010.3378115</v>
       </c>
       <c r="D47" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>882909631.57829285</v>
       </c>
-      <c r="E47">
-        <f t="shared" si="5"/>
-        <v>686204568.70000911</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E47" s="24">
+        <f t="shared" si="6"/>
+        <v>665448989.32055938</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2038</v>
       </c>
       <c r="B48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>38</v>
       </c>
       <c r="C48" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1394791511.7791042</v>
       </c>
       <c r="D48" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>872091836.90853882</v>
       </c>
-      <c r="E48">
-        <f t="shared" si="5"/>
-        <v>677796890.4279145</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E48" s="24">
+        <f t="shared" si="6"/>
+        <v>657295617.47796571</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>2039</v>
       </c>
       <c r="B49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>39</v>
       </c>
       <c r="C49" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1390553676.5213642</v>
       </c>
       <c r="D49" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>861625335.14532471</v>
       </c>
-      <c r="E49">
-        <f t="shared" si="5"/>
-        <v>669662239.868734</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E49" s="24">
+        <f t="shared" si="6"/>
+        <v>649407015.09903121</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>2040</v>
       </c>
       <c r="B50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="C50" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1386108847.999999</v>
       </c>
       <c r="D50" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>851577696</v>
       </c>
-      <c r="E50">
-        <f t="shared" si="5"/>
-        <v>661853132.75338197</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E50" s="24">
+        <f t="shared" si="6"/>
+        <v>641834109.47520006</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>2041</v>
       </c>
       <c r="B51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
       <c r="C51" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1381455009.4141035</v>
       </c>
       <c r="D51" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>841960454.26281738</v>
       </c>
-      <c r="E51">
-        <f t="shared" si="5"/>
-        <v>654378534.01494718</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E51" s="24">
+        <f t="shared" si="6"/>
+        <v>634585594.37788546</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>2042</v>
       </c>
       <c r="B52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
       <c r="C52" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1376584997.9467831</v>
       </c>
       <c r="D52" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>832729923.22790527</v>
       </c>
-      <c r="E52">
-        <f t="shared" si="5"/>
-        <v>647204489.98921692</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E52" s="24">
+        <f t="shared" si="6"/>
+        <v>627628543.13687229</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>2043</v>
       </c>
       <c r="B53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>43</v>
       </c>
       <c r="C53" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1371486829.6736317</v>
       </c>
       <c r="D53" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>823790672.16592407</v>
       </c>
-      <c r="E53">
-        <f t="shared" si="5"/>
-        <v>640256831.13479662</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E53" s="24">
+        <f t="shared" si="6"/>
+        <v>620891029.61145699</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>2044</v>
       </c>
       <c r="B54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>44</v>
       </c>
       <c r="C54" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1366144135.1592941</v>
       </c>
       <c r="D54" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>815001667.84408569</v>
       </c>
-      <c r="E54">
-        <f t="shared" si="5"/>
-        <v>633425945.27257252</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E54" s="24">
+        <f t="shared" si="6"/>
+        <v>614266757.0540874</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>2045</v>
       </c>
       <c r="B55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="C55" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1360536705.7421875</v>
       </c>
       <c r="D55" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>806185080.09375</v>
       </c>
-      <c r="E55">
-        <f t="shared" si="5"/>
-        <v>626573621.34468663</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E55" s="24">
+        <f t="shared" si="6"/>
+        <v>607621694.8666594</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>2046</v>
       </c>
       <c r="B56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="C56" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1354641150.5072956</v>
       </c>
       <c r="D56" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>797137751.42553711</v>
       </c>
-      <c r="E56">
-        <f t="shared" si="5"/>
-        <v>619541963.69297397</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E56" s="24">
+        <f t="shared" si="6"/>
+        <v>600802723.24942732</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>2047</v>
       </c>
       <c r="B57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="C57" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1348431663.9471321</v>
       </c>
       <c r="D57" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>787645330.6920166</v>
       </c>
-      <c r="E57" s="10">
-        <f>D57*$B$75</f>
-        <v>612164376.8569119</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E57" s="24">
+        <f t="shared" si="6"/>
+        <v>593648285.7425729</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>2048</v>
       </c>
       <c r="B58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="C58" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1341880904.3107834</v>
       </c>
       <c r="D58" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>777499070.79785156</v>
       </c>
-      <c r="E58">
-        <f t="shared" si="5"/>
-        <v>604278620.89098394</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E58" s="24">
+        <f t="shared" si="6"/>
+        <v>586001049.66034079</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>2049</v>
       </c>
       <c r="B59">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>49</v>
       </c>
       <c r="C59" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1334960982.6411018</v>
       </c>
       <c r="D59" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>766515290.45739746</v>
       </c>
-      <c r="E59">
-        <f t="shared" si="5"/>
-        <v>595741937.2014612</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E59" s="24">
+        <f t="shared" si="6"/>
+        <v>577722574.41774046</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>2050</v>
       </c>
       <c r="B60">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="C60" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1327644562.5</v>
       </c>
       <c r="D60" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>754557500</v>
       </c>
-      <c r="E60">
-        <f t="shared" si="5"/>
-        <v>586448244.90278816</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E60" s="24">
+        <f t="shared" si="6"/>
+        <v>568709987.75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>2051</v>
       </c>
       <c r="B61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>51</v>
       </c>
       <c r="C61" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1319906070.3818645</v>
       </c>
       <c r="D61" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>741561191.22283936</v>
       </c>
-      <c r="E61">
-        <f t="shared" si="5"/>
-        <v>576347407.69345605</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E61" s="24">
+        <f t="shared" si="6"/>
+        <v>558914669.8246541</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>2052</v>
       </c>
       <c r="B62">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>52</v>
       </c>
       <c r="C62" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1311723016.8151016</v>
       </c>
       <c r="D62" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>727561291.29064941</v>
       </c>
-      <c r="E62">
-        <f t="shared" si="5"/>
-        <v>565466571.25084245</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E62" s="24">
+        <f t="shared" si="6"/>
+        <v>548362945.24576247</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>2053</v>
       </c>
       <c r="B63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>53</v>
       </c>
       <c r="C63" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1303077428.1518135</v>
       </c>
       <c r="D63" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>712722280.6842041</v>
       </c>
-      <c r="E63">
-        <f t="shared" si="5"/>
-        <v>553933571.14648497</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E63" s="24">
+        <f t="shared" si="6"/>
+        <v>537178782.95168471</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>2054</v>
       </c>
       <c r="B64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>54</v>
       </c>
       <c r="C64" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1293957389.045536</v>
       </c>
       <c r="D64" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>697370975.19512939</v>
       </c>
-      <c r="E64">
-        <f t="shared" si="5"/>
-        <v>542002411.27989507</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E64" s="24">
+        <f t="shared" si="6"/>
+        <v>525608504.00456905</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>2055</v>
       </c>
       <c r="B65">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>55</v>
       </c>
       <c r="C65" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1284358695.6171837</v>
       </c>
       <c r="D65" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>682031971.96875</v>
       </c>
-      <c r="E65">
-        <f t="shared" si="5"/>
-        <v>530080812.83223748</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E65" s="24">
+        <f t="shared" si="6"/>
+        <v>514047497.27284688</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>2056</v>
       </c>
       <c r="B66">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>56</v>
       </c>
       <c r="C66" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1274286619.3090515</v>
       </c>
       <c r="D66" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>667465759.59448242</v>
       </c>
-      <c r="E66">
-        <f t="shared" si="5"/>
-        <v>518759833.73949701</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E66" s="24">
+        <f t="shared" si="6"/>
+        <v>503068943.00636142</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>2057</v>
       </c>
       <c r="B67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>57</v>
       </c>
       <c r="C67" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1263757781.4269485</v>
       </c>
       <c r="D67" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>654709492.24377441</v>
       </c>
-      <c r="E67">
-        <f t="shared" si="5"/>
-        <v>508845558.6851328</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E67" s="24">
+        <f t="shared" si="6"/>
+        <v>493454544.30413282</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>2058</v>
       </c>
       <c r="B68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>58</v>
       </c>
       <c r="C68" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1252802138.3704605</v>
       </c>
       <c r="D68" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>645120427.85510254</v>
       </c>
-      <c r="E68">
-        <f t="shared" si="5"/>
-        <v>501392859.61183953</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E68" s="24">
+        <f t="shared" si="6"/>
+        <v>486227266.4743908</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>2059</v>
       </c>
       <c r="B69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>59</v>
       </c>
       <c r="C69" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1241465077.5513382</v>
       </c>
       <c r="D69" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>640422030.36743164</v>
       </c>
-      <c r="E69">
-        <f t="shared" si="5"/>
-        <v>497741226.75350833</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E69" s="24">
+        <f t="shared" si="6"/>
+        <v>482686084.28793323</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>2060</v>
       </c>
       <c r="B70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="C70" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1229809624</v>
       </c>
       <c r="D70" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>642752736</v>
       </c>
-      <c r="E70">
-        <f t="shared" si="5"/>
-        <v>499552670.18572491</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E70" s="24">
+        <f>D70*$B$81</f>
+        <v>484442737.1232</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="21" t="s">
         <v>94</v>
       </c>
@@ -5496,7 +5563,7 @@
         <v>972809418.79524612</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="21" t="s">
         <v>95</v>
       </c>
@@ -5504,18 +5571,69 @@
         <v>756075416.75402272</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="22">
         <f>B73/B72</f>
         <v>0.777208158295144</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B75">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B75" s="22">
         <v>0.777208158295144</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B76" s="23">
+        <v>0.77559999999999996</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B77" s="23">
+        <v>0.77339999999999998</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B78" s="23">
+        <v>0.76219999999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B79" s="23">
+        <v>0.77180000000000004</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B80" s="22">
+        <v>0.76049999999999995</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B81" s="23">
+        <v>0.75370000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -5528,17 +5646,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="12.6640625"/>
-    <col min="5" max="5" width="12.6640625"/>
-    <col min="7" max="7" width="12.6640625"/>
-    <col min="9" max="9" width="12.6640625"/>
-    <col min="12" max="12" width="12.6640625"/>
-    <col min="15" max="15" width="12.6640625"/>
+    <col min="3" max="3" width="12.625"/>
+    <col min="5" max="5" width="12.625"/>
+    <col min="7" max="7" width="12.625"/>
+    <col min="9" max="9" width="12.625"/>
+    <col min="12" max="12" width="12.625"/>
+    <col min="15" max="15" width="12.625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>56</v>
       </c>
@@ -5567,7 +5685,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:15" ht="13.9" x14ac:dyDescent="0.15">
       <c r="A2" s="8">
         <v>2010</v>
       </c>
@@ -5602,7 +5720,7 @@
         <v>9477713619655.707</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:15" ht="13.9" x14ac:dyDescent="0.15">
       <c r="A3" s="8">
         <v>2011</v>
       </c>
@@ -5631,17 +5749,17 @@
       </c>
       <c r="L3">
         <f>I3*就业人口计算!E30</f>
-        <v>73096572559999.969</v>
+        <v>72945324971751.766</v>
       </c>
       <c r="N3">
         <v>2020</v>
       </c>
       <c r="O3">
         <f>L3*汇率!B22</f>
-        <v>10061792771500.137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
+        <v>10040973438433.686</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="13.9" x14ac:dyDescent="0.15">
       <c r="A4" s="8">
         <v>2012</v>
       </c>
@@ -5671,17 +5789,17 @@
       </c>
       <c r="L4">
         <f>I4*就业人口计算!E31</f>
-        <v>78545390358218.766</v>
+        <v>78160534285047.719</v>
       </c>
       <c r="N4">
         <v>2021</v>
       </c>
       <c r="O4">
         <f>L4*汇率!B23</f>
-        <v>10579086336261.557</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+        <v>10527251013952.471</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="13.9" x14ac:dyDescent="0.15">
       <c r="A5" s="8">
         <v>2013</v>
       </c>
@@ -5711,17 +5829,17 @@
       </c>
       <c r="L5">
         <f>I5*就业人口计算!E32</f>
-        <v>84641226914503.5</v>
+        <v>83006775553860.844</v>
       </c>
       <c r="N5">
         <v>2022</v>
       </c>
       <c r="O5">
         <f>L5*汇率!B24</f>
-        <v>11154715888934.023</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
+        <v>10939314467819.623</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="13.9" x14ac:dyDescent="0.15">
       <c r="A6" s="8">
         <v>2014</v>
       </c>
@@ -5751,17 +5869,17 @@
       </c>
       <c r="L6">
         <f>I6*就业人口计算!E33</f>
-        <v>91334231366052</v>
+        <v>90698687367033.234</v>
       </c>
       <c r="N6">
         <v>2023</v>
       </c>
       <c r="O6">
         <f>L6*汇率!B25</f>
-        <v>11777666314251.479</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
+        <v>11695712100190.504</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="13.9" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
         <v>2015</v>
       </c>
@@ -5791,17 +5909,17 @@
       </c>
       <c r="L7">
         <f>I7*就业人口计算!E34</f>
-        <v>98577851142513.938</v>
+        <v>96458657817398.594</v>
       </c>
       <c r="N7">
         <v>2024</v>
       </c>
       <c r="O7">
         <f>L7*汇率!B26</f>
-        <v>12438102130933.826</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
+        <v>12170712015329.957</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="13.9" x14ac:dyDescent="0.15">
       <c r="A8" s="8">
         <v>2016</v>
       </c>
@@ -5831,17 +5949,17 @@
       </c>
       <c r="L8">
         <f>I8*就业人口计算!E35</f>
-        <v>106330410571744.86</v>
+        <v>103114242423444.23</v>
       </c>
       <c r="N8">
         <v>2025</v>
       </c>
       <c r="O8">
         <f>L8*汇率!B27</f>
-        <v>13127480040440.092</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
+        <v>12730414112202.863</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="13.9" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
         <v>2017</v>
       </c>
@@ -5871,17 +5989,17 @@
       </c>
       <c r="L9">
         <f>I9*就业人口计算!E36</f>
-        <v>114556710303992.52</v>
+        <v>111091721869614.11</v>
       </c>
       <c r="N9">
         <v>2026</v>
       </c>
       <c r="O9">
         <f>L9*汇率!B28</f>
-        <v>13838643248878.334</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
+        <v>13420066819111.73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="13.9" x14ac:dyDescent="0.15">
       <c r="A10" s="8">
         <v>2018</v>
       </c>
@@ -5911,17 +6029,17 @@
       </c>
       <c r="L10">
         <f>I10*就业人口计算!E37</f>
-        <v>123229606799129.72</v>
+        <v>119502289899064.2</v>
       </c>
       <c r="N10">
         <v>2027</v>
       </c>
       <c r="O10">
         <f>L10*汇率!B29</f>
-        <v>14565894060916.844</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
+        <v>14125320529051.912</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="13.9" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>2019</v>
       </c>
@@ -5951,17 +6069,17 @@
       </c>
       <c r="L11">
         <f>I11*就业人口计算!E38</f>
-        <v>132331524079891.84</v>
+        <v>128328902153828.11</v>
       </c>
       <c r="N11">
         <v>2028</v>
       </c>
       <c r="O11">
         <f>L11*汇率!B30</f>
-        <v>15305041191632.883</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
+        <v>14842110730589.043</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="13.9" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>2020</v>
       </c>
@@ -5991,17 +6109,17 @@
       </c>
       <c r="L12">
         <f>I12*就业人口计算!E39</f>
-        <v>141855842855555.94</v>
+        <v>137565139556385.08</v>
       </c>
       <c r="N12">
         <v>2029</v>
       </c>
       <c r="O12">
         <f>L12*汇率!B31</f>
-        <v>16053418263175.684</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>15567851695608.109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="H13">
         <v>2030</v>
       </c>
@@ -6014,17 +6132,17 @@
       </c>
       <c r="L13">
         <f>I13*就业人口计算!E40</f>
-        <v>151808105218912.94</v>
+        <v>147216376568250.88</v>
       </c>
       <c r="N13">
         <v>2030</v>
       </c>
       <c r="O13">
         <f>L13*汇率!B32</f>
-        <v>16809870066079.166</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>16301423156179.219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>1.0509999999999999</v>
       </c>
@@ -6040,17 +6158,17 @@
       </c>
       <c r="L14">
         <f>I14*就业人口计算!E41</f>
-        <v>162206966748720.19</v>
+        <v>157300704494257.31</v>
       </c>
       <c r="N14">
         <v>2031</v>
       </c>
       <c r="O14">
         <f>L14*汇率!B33</f>
-        <v>17574703391078.051</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>17043122623560.201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="H15">
         <v>2032</v>
       </c>
@@ -6063,17 +6181,17 @@
       </c>
       <c r="L15">
         <f>I15*就业人口计算!E42</f>
-        <v>173084822441738.19</v>
+        <v>167849538482068.16</v>
       </c>
       <c r="N15">
         <v>2032</v>
       </c>
       <c r="O15">
         <f>L15*汇率!B34</f>
-        <v>18349599600685.863</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>17794580604215.652</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="H16">
         <v>2033</v>
       </c>
@@ -6086,17 +6204,17 @@
       </c>
       <c r="L16">
         <f>I16*就业人口计算!E43</f>
-        <v>184488029002420.81</v>
+        <v>178907833088289.56</v>
       </c>
       <c r="N16">
         <v>2033</v>
       </c>
       <c r="O16">
         <f>L16*汇率!B35</f>
-        <v>19137486638604.605</v>
-      </c>
-    </row>
-    <row r="17" spans="8:15" x14ac:dyDescent="0.25">
+        <v>18558636480548.648</v>
+      </c>
+    </row>
+    <row r="17" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H17">
         <v>2034</v>
       </c>
@@ -6109,17 +6227,17 @@
       </c>
       <c r="L17">
         <f>I17*就业人口计算!E44</f>
-        <v>196476644325052.13</v>
+        <v>190533829640471.78</v>
       </c>
       <c r="N17">
         <v>2034</v>
       </c>
       <c r="O17">
         <f>L17*汇率!B36</f>
-        <v>19942368901402.176</v>
-      </c>
-    </row>
-    <row r="18" spans="8:15" x14ac:dyDescent="0.25">
+        <v>19339173528437.125</v>
+      </c>
+    </row>
+    <row r="18" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H18">
         <v>2035</v>
       </c>
@@ -6132,17 +6250,17 @@
       </c>
       <c r="L18">
         <f>I18*就业人口计算!E45</f>
-        <v>209123606373188.69</v>
+        <v>202798259952924.5</v>
       </c>
       <c r="N18">
         <v>2035</v>
       </c>
       <c r="O18">
         <f>L18*汇率!B37</f>
-        <v>20769114357701.492</v>
-      </c>
-    </row>
-    <row r="19" spans="8:15" x14ac:dyDescent="0.25">
+        <v>20140912475413.242</v>
+      </c>
+    </row>
+    <row r="19" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H19">
         <v>2036</v>
       </c>
@@ -6155,17 +6273,17 @@
       </c>
       <c r="L19">
         <f>I19*就业人口计算!E46</f>
-        <v>222513279156007.97</v>
+        <v>215782936282812.63</v>
       </c>
       <c r="N19">
         <v>2036</v>
       </c>
       <c r="O19">
         <f>L19*汇率!B38</f>
-        <v>21623199537405.582</v>
-      </c>
-    </row>
-    <row r="20" spans="8:15" x14ac:dyDescent="0.25">
+        <v>20969164203180.77</v>
+      </c>
+    </row>
+    <row r="20" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H20">
         <v>2037</v>
       </c>
@@ -6178,17 +6296,17 @@
       </c>
       <c r="L20">
         <f>I20*就业人口计算!E47</f>
-        <v>236739304422566.25</v>
+        <v>229578668004060.53</v>
       </c>
       <c r="N20">
         <v>2037</v>
       </c>
       <c r="O20">
         <f>L20*汇率!B39</f>
-        <v>22510414575272.332</v>
-      </c>
-    </row>
-    <row r="21" spans="8:15" x14ac:dyDescent="0.25">
+        <v>21829543712715.246</v>
+      </c>
+    </row>
+    <row r="21" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H21">
         <v>2038</v>
       </c>
@@ -6201,17 +6319,17 @@
       </c>
       <c r="L21">
         <f>I21*就业人口计算!E48</f>
-        <v>251901715627727.5</v>
+        <v>244282462866942.44</v>
       </c>
       <c r="N21">
         <v>2038</v>
       </c>
       <c r="O21">
         <f>L21*汇率!B40</f>
-        <v>23436532433989.188</v>
-      </c>
-    </row>
-    <row r="22" spans="8:15" x14ac:dyDescent="0.25">
+        <v>22727649352324.117</v>
+      </c>
+    </row>
+    <row r="22" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H22">
         <v>2039</v>
       </c>
@@ -6224,17 +6342,17 @@
       </c>
       <c r="L22">
         <f>I22*就业人口计算!E49</f>
-        <v>268103297587148.94</v>
+        <v>259993996762317.16</v>
       </c>
       <c r="N22">
         <v>2039</v>
       </c>
       <c r="O22">
         <f>L22*汇率!B41</f>
-        <v>24406948813717.52</v>
-      </c>
-    </row>
-    <row r="23" spans="8:15" x14ac:dyDescent="0.25">
+        <v>23668713618820.785</v>
+      </c>
+    </row>
+    <row r="23" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H23">
         <v>2040</v>
       </c>
@@ -6247,17 +6365,17 @@
       </c>
       <c r="L23">
         <f>I23*就业人口计算!E50</f>
-        <v>285445213347458.63</v>
+        <v>276811372865543.69</v>
       </c>
       <c r="N23">
         <v>2040</v>
       </c>
       <c r="O23">
         <f>L23*汇率!B42</f>
-        <v>25426302148134.738</v>
-      </c>
-    </row>
-    <row r="24" spans="8:15" x14ac:dyDescent="0.25">
+        <v>24657234647518.613</v>
+      </c>
+    </row>
+    <row r="24" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H24">
         <v>2041</v>
       </c>
@@ -6270,17 +6388,17 @@
       </c>
       <c r="L24">
         <f>I24*就业人口计算!E51</f>
-        <v>304021971927025.06</v>
+        <v>294826241587627</v>
       </c>
       <c r="N24">
         <v>2041</v>
       </c>
       <c r="O24">
         <f>L24*汇率!B43</f>
-        <v>26498086570621.102</v>
-      </c>
-    </row>
-    <row r="25" spans="8:15" x14ac:dyDescent="0.25">
+        <v>25696600885001.168</v>
+      </c>
+    </row>
+    <row r="25" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H25">
         <v>2042</v>
       </c>
@@ -6293,17 +6411,17 @@
       </c>
       <c r="L25">
         <f>I25*就业人口计算!E52</f>
-        <v>323915880051217.56</v>
+        <v>314118420128436.88</v>
       </c>
       <c r="N25">
         <v>2042</v>
       </c>
       <c r="O25">
         <f>L25*汇率!B44</f>
-        <v>27624274898147.832</v>
-      </c>
-    </row>
-    <row r="26" spans="8:15" x14ac:dyDescent="0.25">
+        <v>26788725476589.105</v>
+      </c>
+    </row>
+    <row r="26" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H26">
         <v>2043</v>
       </c>
@@ -6316,17 +6434,17 @@
       </c>
       <c r="L26">
         <f>I26*就业人口计算!E53</f>
-        <v>345191211765367.69</v>
+        <v>334750238440958.44</v>
       </c>
       <c r="N26">
         <v>2043</v>
       </c>
       <c r="O26">
         <f>L26*汇率!B45</f>
-        <v>28804973625731.707</v>
-      </c>
-    </row>
-    <row r="27" spans="8:15" x14ac:dyDescent="0.25">
+        <v>27933711696152.219</v>
+      </c>
+    </row>
+    <row r="27" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H27">
         <v>2044</v>
       </c>
@@ -6339,17 +6457,17 @@
       </c>
       <c r="L27">
         <f>I27*就业人口计算!E54</f>
-        <v>367888446549038.13</v>
+        <v>356760951624898.13</v>
       </c>
       <c r="N27">
         <v>2044</v>
       </c>
       <c r="O27">
         <f>L27*汇率!B46</f>
-        <v>30038137764849.738</v>
-      </c>
-    </row>
-    <row r="28" spans="8:15" x14ac:dyDescent="0.25">
+        <v>29129576409785.738</v>
+      </c>
+    </row>
+    <row r="28" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H28">
         <v>2045</v>
       </c>
@@ -6362,17 +6480,17 @@
       </c>
       <c r="L28">
         <f>I28*就业人口计算!E55</f>
-        <v>392019074828738.25</v>
+        <v>380161702556675.38</v>
       </c>
       <c r="N28">
         <v>2045</v>
       </c>
       <c r="O28">
         <f>L28*汇率!B47</f>
-        <v>31319380223052.77</v>
-      </c>
-    </row>
-    <row r="29" spans="8:15" x14ac:dyDescent="0.25">
+        <v>30372065221104.82</v>
+      </c>
+    </row>
+    <row r="29" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H29">
         <v>2046</v>
       </c>
@@ -6385,17 +6503,17 @@
       </c>
       <c r="L29">
         <f>I29*就业人口计算!E56</f>
-        <v>417561656143948.88</v>
+        <v>404931699283811.56</v>
       </c>
       <c r="N29">
         <v>2046</v>
       </c>
       <c r="O29">
         <f>L29*汇率!B48</f>
-        <v>32641918452907.676</v>
-      </c>
-    </row>
-    <row r="30" spans="8:15" x14ac:dyDescent="0.25">
+        <v>31654600733892.258</v>
+      </c>
+    </row>
+    <row r="30" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H30">
         <v>2047</v>
       </c>
@@ -6408,17 +6526,17 @@
       </c>
       <c r="L30">
         <f>I30*就业人口计算!E57</f>
-        <v>444460047376289.25</v>
+        <v>431016496844719.56</v>
       </c>
       <c r="N30">
         <v>2047</v>
       </c>
       <c r="O30">
         <f>L30*汇率!B49</f>
-        <v>33996710457655.945</v>
-      </c>
-    </row>
-    <row r="31" spans="8:15" x14ac:dyDescent="0.25">
+        <v>32968414444003.891</v>
+      </c>
+    </row>
+    <row r="31" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H31">
         <v>2048</v>
       </c>
@@ -6431,17 +6549,17 @@
       </c>
       <c r="L31">
         <f>I31*就业人口计算!E58</f>
-        <v>472625005461308</v>
+        <v>458329551503388.5</v>
       </c>
       <c r="N31">
         <v>2048</v>
       </c>
       <c r="O31">
         <f>L31*汇率!B50</f>
-        <v>35372843109278.789</v>
-      </c>
-    </row>
-    <row r="32" spans="8:15" x14ac:dyDescent="0.25">
+        <v>34302923312005.594</v>
+      </c>
+    </row>
+    <row r="32" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H32">
         <v>2049</v>
       </c>
@@ -6454,17 +6572,17 @@
       </c>
       <c r="L32">
         <f>I32*就业人口计算!E59</f>
-        <v>501940721480872.94</v>
+        <v>486758557205559</v>
       </c>
       <c r="N32">
         <v>2049</v>
       </c>
       <c r="O32">
         <f>L32*汇率!B51</f>
-        <v>36758248314259.617</v>
-      </c>
-    </row>
-    <row r="33" spans="8:15" x14ac:dyDescent="0.25">
+        <v>35646424267122.336</v>
+      </c>
+    </row>
+    <row r="33" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H33">
         <v>2050</v>
       </c>
@@ -6477,17 +6595,17 @@
       </c>
       <c r="L33">
         <f>I33*就业人口计算!E60</f>
-        <v>532278273393191.25</v>
+        <v>516178491405003</v>
       </c>
       <c r="N33">
         <v>2050</v>
       </c>
       <c r="O33">
         <f>L33*汇率!B52</f>
-        <v>38140837079322.844</v>
-      </c>
-    </row>
-    <row r="34" spans="8:15" x14ac:dyDescent="0.25">
+        <v>36987193970973.57</v>
+      </c>
+    </row>
+    <row r="34" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H34">
         <v>2051</v>
       </c>
@@ -6500,17 +6618,17 @@
       </c>
       <c r="L34">
         <f>I34*就业人口计算!E61</f>
-        <v>563518507382602.38</v>
+        <v>546473804322804.13</v>
       </c>
       <c r="N34">
         <v>2051</v>
       </c>
       <c r="O34">
         <f>L34*汇率!B53</f>
-        <v>39510158236278.445</v>
-      </c>
-    </row>
-    <row r="35" spans="8:15" x14ac:dyDescent="0.25">
+        <v>38315097371088.844</v>
+      </c>
+    </row>
+    <row r="35" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H35">
         <v>2052</v>
       </c>
@@ -6523,17 +6641,17 @@
       </c>
       <c r="L35">
         <f>I35*就业人口计算!E62</f>
-        <v>595587489778647.38</v>
+        <v>577572798554823.38</v>
       </c>
       <c r="N35">
         <v>2052</v>
       </c>
       <c r="O35">
         <f>L35*汇率!B54</f>
-        <v>40859707763576.211</v>
-      </c>
-    </row>
-    <row r="36" spans="8:15" x14ac:dyDescent="0.25">
+        <v>39623827172581.805</v>
+      </c>
+    </row>
+    <row r="36" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H36">
         <v>2053</v>
       </c>
@@ -6546,17 +6664,17 @@
       </c>
       <c r="L36">
         <f>I36*就业人口计算!E63</f>
-        <v>628508432333073</v>
+        <v>609497983768651.38</v>
       </c>
       <c r="N36">
         <v>2053</v>
       </c>
       <c r="O36">
         <f>L36*汇率!B55</f>
-        <v>42190036606538.18</v>
-      </c>
-    </row>
-    <row r="37" spans="8:15" x14ac:dyDescent="0.25">
+        <v>40913917656371.703</v>
+      </c>
+    </row>
+    <row r="37" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H37">
         <v>2054</v>
       </c>
@@ -6569,17 +6687,17 @@
       </c>
       <c r="L37">
         <f>I37*就业人口计算!E64</f>
-        <v>662474906135906.5</v>
+        <v>642437076123718.88</v>
       </c>
       <c r="N37">
         <v>2054</v>
       </c>
       <c r="O37">
         <f>L37*汇率!B56</f>
-        <v>43512829997786.938</v>
-      </c>
-    </row>
-    <row r="38" spans="8:15" x14ac:dyDescent="0.25">
+        <v>42196700612704.992</v>
+      </c>
+    </row>
+    <row r="38" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H38">
         <v>2055</v>
       </c>
@@ -6592,17 +6710,17 @@
       </c>
       <c r="L38">
         <f>I38*就业人口计算!E65</f>
-        <v>697951250028817.63</v>
+        <v>676840369638727.38</v>
       </c>
       <c r="N38">
         <v>2055</v>
       </c>
       <c r="O38">
         <f>L38*汇率!B57</f>
-        <v>44856159904210.891</v>
-      </c>
-    </row>
-    <row r="39" spans="8:15" x14ac:dyDescent="0.25">
+        <v>43499398917741.625</v>
+      </c>
+    </row>
+    <row r="39" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H39">
         <v>2056</v>
       </c>
@@ -6615,17 +6733,17 @@
       </c>
       <c r="L39">
         <f>I39*就业人口计算!E66</f>
-        <v>735807378610097.5</v>
+        <v>713551466668766.13</v>
       </c>
       <c r="N39">
         <v>2056</v>
       </c>
       <c r="O39">
         <f>L39*汇率!B58</f>
-        <v>46271144809018.586</v>
-      </c>
-    </row>
-    <row r="40" spans="8:15" x14ac:dyDescent="0.25">
+        <v>44871584877668.945</v>
+      </c>
+    </row>
+    <row r="40" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H40">
         <v>2057</v>
       </c>
@@ -6638,17 +6756,17 @@
       </c>
       <c r="L40">
         <f>I40*就业人口计算!E67</f>
-        <v>777496738184844.5</v>
+        <v>753979851234892.38</v>
       </c>
       <c r="N40">
         <v>2057</v>
       </c>
       <c r="O40">
         <f>L40*汇率!B59</f>
-        <v>47840288058435.672</v>
-      </c>
-    </row>
-    <row r="41" spans="8:15" x14ac:dyDescent="0.25">
+        <v>46393266366036.109</v>
+      </c>
+    </row>
+    <row r="41" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H41">
         <v>2058</v>
       </c>
@@ -6661,17 +6779,17 @@
       </c>
       <c r="L41">
         <f>I41*就业人口计算!E68</f>
-        <v>825287987115065.63</v>
+        <v>800325561755636.88</v>
       </c>
       <c r="N41">
         <v>2058</v>
       </c>
       <c r="O41">
         <f>L41*汇率!B60</f>
-        <v>49687807996161.93</v>
-      </c>
-    </row>
-    <row r="42" spans="8:15" x14ac:dyDescent="0.25">
+        <v>48184904503390.148</v>
+      </c>
+    </row>
+    <row r="42" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H42">
         <v>2059</v>
       </c>
@@ -6684,17 +6802,17 @@
       </c>
       <c r="L42">
         <f>I42*就业人口计算!E69</f>
-        <v>882563137041608.38</v>
+        <v>855868314413210</v>
       </c>
       <c r="N42">
         <v>2059</v>
       </c>
       <c r="O42">
         <f>L42*汇率!B61</f>
-        <v>51992320667465.617</v>
-      </c>
-    </row>
-    <row r="43" spans="8:15" x14ac:dyDescent="0.25">
+        <v>50419712748547.547</v>
+      </c>
+    </row>
+    <row r="43" spans="8:15" x14ac:dyDescent="0.2">
       <c r="H43">
         <v>2060</v>
       </c>
@@ -6707,14 +6825,14 @@
       </c>
       <c r="L43">
         <f>I43*就业人口计算!E70</f>
-        <v>954197437584864.25</v>
+        <v>925335897509460.88</v>
       </c>
       <c r="N43">
         <v>2060</v>
       </c>
       <c r="O43">
         <f>L43*汇率!B62</f>
-        <v>55002289654939.828</v>
+        <v>53338639424298.953</v>
       </c>
     </row>
   </sheetData>
@@ -6727,13 +6845,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AQ2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="43" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="43" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>65</v>
       </c>
@@ -6864,7 +6982,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:43" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>66</v>
       </c>
@@ -7004,14 +7122,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AQ2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.625" customWidth="1"/>
+    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>65</v>
       </c>
@@ -7142,135 +7260,136 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" cm="1">
+        <f t="array" ref="B2:AQ2">TRANSPOSE(就业人口计算!E29:E70)</f>
         <v>756075416.75402272</v>
       </c>
       <c r="C2">
-        <v>750640000</v>
+        <v>749086815.14239991</v>
       </c>
       <c r="D2">
-        <v>748756491.72068906</v>
+        <v>745087740.67303646</v>
       </c>
       <c r="E2">
-        <v>749009036.11495101</v>
+        <v>734545412.62035847</v>
       </c>
       <c r="F2">
-        <v>750280905.80221403</v>
+        <v>745060119.24574816</v>
       </c>
       <c r="G2">
-        <v>751717864.67263901</v>
+        <v>735557688.09421813</v>
       </c>
       <c r="H2">
-        <v>752693601.25675905</v>
+        <v>729926932.97460938</v>
       </c>
       <c r="I2">
-        <v>752777232.614622</v>
+        <v>730008034.74091029</v>
       </c>
       <c r="J2">
-        <v>751702878.744326</v>
+        <v>728966176.77351773</v>
       </c>
       <c r="K2">
-        <v>749341307.510095</v>
+        <v>726676035.8116107</v>
       </c>
       <c r="L2">
-        <v>745673650.08977902</v>
+        <v>723119313.75692225</v>
       </c>
       <c r="M2">
-        <v>740767186.94182897</v>
+        <v>718361256.04079998</v>
       </c>
       <c r="N2">
-        <v>734753204.29175103</v>
+        <v>712529177.88389146</v>
       </c>
       <c r="O2">
-        <v>727806921.13797796</v>
+        <v>705792998.4484067</v>
       </c>
       <c r="P2">
-        <v>720129486.77733696</v>
+        <v>698347782.88310969</v>
       </c>
       <c r="Q2">
-        <v>711932048.84978795</v>
+        <v>690398292.26074362</v>
       </c>
       <c r="R2">
-        <v>703421891.90280998</v>
+        <v>682145541.40824687</v>
       </c>
       <c r="S2">
-        <v>694790646.47514498</v>
+        <v>673775364.62947929</v>
       </c>
       <c r="T2">
-        <v>686204568.70000899</v>
+        <v>665448989.32055938</v>
       </c>
       <c r="U2">
-        <v>677796890.42791498</v>
+        <v>657295617.47796571</v>
       </c>
       <c r="V2">
-        <v>669662239.868734</v>
+        <v>649407015.09903121</v>
       </c>
       <c r="W2">
-        <v>661853132.75338197</v>
+        <v>641834109.47520006</v>
       </c>
       <c r="X2">
-        <v>654378534.01494801</v>
+        <v>634585594.37788546</v>
       </c>
       <c r="Y2">
-        <v>647204489.98921704</v>
+        <v>627628543.13687229</v>
       </c>
       <c r="Z2">
-        <v>640256831.13479698</v>
+        <v>620891029.61145699</v>
       </c>
       <c r="AA2">
-        <v>633425945.27257299</v>
+        <v>614266757.0540874</v>
       </c>
       <c r="AB2">
-        <v>626573621.34468699</v>
+        <v>607621694.8666594</v>
       </c>
       <c r="AC2">
-        <v>619541963.69297397</v>
+        <v>600802723.24942732</v>
       </c>
       <c r="AD2">
-        <v>612164376.85691202</v>
+        <v>593648285.7425729</v>
       </c>
       <c r="AE2">
-        <v>604278620.89098406</v>
+        <v>586001049.66034079</v>
       </c>
       <c r="AF2">
-        <v>595741937.20146203</v>
+        <v>577722574.41774046</v>
       </c>
       <c r="AG2">
-        <v>586448244.90278804</v>
+        <v>568709987.75</v>
       </c>
       <c r="AH2">
-        <v>576347407.69345605</v>
+        <v>558914669.8246541</v>
       </c>
       <c r="AI2">
-        <v>565466571.25084305</v>
+        <v>548362945.24576247</v>
       </c>
       <c r="AJ2">
-        <v>553933571.14648497</v>
+        <v>537178782.95168471</v>
       </c>
       <c r="AK2">
-        <v>542002411.27989495</v>
+        <v>525608504.00456905</v>
       </c>
       <c r="AL2">
-        <v>530080812.83223802</v>
+        <v>514047497.27284688</v>
       </c>
       <c r="AM2">
-        <v>518759833.73949701</v>
+        <v>503068943.00636142</v>
       </c>
       <c r="AN2">
-        <v>508845558.68513298</v>
+        <v>493454544.30413282</v>
       </c>
       <c r="AO2">
-        <v>501392859.61184001</v>
+        <v>486227266.4743908</v>
       </c>
       <c r="AP2">
-        <v>497741226.75350899</v>
+        <v>482686084.28793323</v>
       </c>
       <c r="AQ2">
-        <v>499552670.18572497</v>
+        <v>484442737.1232</v>
       </c>
     </row>
   </sheetData>
@@ -7282,9 +7401,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AQ2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>68</v>
       </c>
@@ -7415,7 +7534,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>69</v>
       </c>
@@ -7555,9 +7674,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
@@ -7565,7 +7684,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>72</v>
       </c>
@@ -7574,7 +7693,7 @@
         <v>0.26402731839314603</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>73</v>
       </c>
@@ -7583,7 +7702,7 @@
         <v>0.25873096752649299</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>74</v>
       </c>
@@ -7592,7 +7711,7 @@
         <v>0.25718247422042501</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>75</v>
       </c>
@@ -7601,7 +7720,7 @@
         <v>0.25065741621071402</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>76</v>
       </c>
@@ -7610,7 +7729,7 @@
         <v>0.234364418959083</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>77</v>
       </c>
@@ -7619,7 +7738,7 @@
         <v>0.22555916594478401</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>78</v>
       </c>
@@ -7628,7 +7747,7 @@
         <v>0.217037097117422</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>79</v>
       </c>
@@ -7637,7 +7756,7 @@
         <v>0.20142712631579199</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>80</v>
       </c>
@@ -7646,7 +7765,7 @@
         <v>0.186860689001348</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>81</v>
       </c>
@@ -7655,7 +7774,7 @@
         <v>0.187253046603439</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>82</v>
       </c>
@@ -7664,7 +7783,7 @@
         <v>0.17519707002278201</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>83</v>
       </c>
@@ -7673,7 +7792,7 @@
         <v>0.16210590836123601</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>84</v>
       </c>
@@ -7682,7 +7801,7 @@
         <v>0.158412957650193</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>85</v>
       </c>
@@ -7691,7 +7810,7 @@
         <v>0.15505846920337699</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>86</v>
       </c>
@@ -7700,7 +7819,7 @@
         <v>0.15347603355213099</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>87</v>
       </c>
@@ -7709,7 +7828,7 @@
         <v>0.153480552163204</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>88</v>
       </c>
@@ -7718,7 +7837,7 @@
         <v>0.15135052654071199</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>89</v>
       </c>
@@ -7727,7 +7846,7 @@
         <v>0.14520448257929899</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>90</v>
       </c>
@@ -7736,7 +7855,7 @@
         <v>0.14029452814745599</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>91</v>
       </c>
@@ -7745,7 +7864,7 @@
         <v>0.138511262027254</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>92</v>
       </c>
@@ -7754,7 +7873,7 @@
         <v>0.13765067798823399</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>2021</v>
       </c>
@@ -7763,7 +7882,7 @@
         <v>0.13468755184758707</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>2022</v>
       </c>
@@ -7772,7 +7891,7 @@
         <v>0.13178821120116152</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>2023</v>
       </c>
@@ -7781,7 +7900,7 @@
         <v>0.12895128297569619</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>2024</v>
       </c>
@@ -7790,7 +7909,7 @@
         <v>0.12617542365528003</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>2025</v>
       </c>
@@ -7799,7 +7918,7 @@
         <v>0.12345931864508809</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>2026</v>
       </c>
@@ -7808,7 +7927,7 @@
         <v>0.12080168164881418</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>2027</v>
       </c>
@@ -7817,7 +7936,7 @@
         <v>0.11820125405950506</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>2028</v>
       </c>
@@ -7826,7 +7945,7 @@
         <v>0.11565680436350788</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>2029</v>
       </c>
@@ -7835,7 +7954,7 @@
         <v>0.11316712755724841</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>2030</v>
       </c>
@@ -7844,7 +7963,7 @@
         <v>0.11073104457656399</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>2031</v>
       </c>
@@ -7853,7 +7972,7 @@
         <v>0.10834740173832093</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>2032</v>
       </c>
@@ -7862,7 +7981,7 @@
         <v>0.10601507019405179</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>2033</v>
       </c>
@@ -7871,7 +7990,7 @@
         <v>0.10373294539535401</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>2034</v>
       </c>
@@ -7880,7 +7999,7 @@
         <v>0.10149994657079649</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>2035</v>
       </c>
@@ -7889,7 +8008,7 @@
         <v>9.9315016214086574E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>2036</v>
       </c>
@@ -7898,7 +8017,7 @@
         <v>9.7177119583254964E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>2037</v>
       </c>
@@ -7907,7 +8026,7 @@
         <v>9.5085244210621298E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>2038</v>
       </c>
@@ -7916,7 +8035,7 @@
         <v>9.3038399423308507E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>2039</v>
       </c>
@@ -7925,7 +8044,7 @@
         <v>9.1035615874078768E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>2040</v>
       </c>
@@ -7934,7 +8053,7 @@
         <v>8.9075945082268848E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>2041</v>
       </c>
@@ -7943,7 +8062,7 @@
         <v>8.7158458984607487E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>2042</v>
       </c>
@@ -7952,7 +8071,7 @@
         <v>8.5282249495702039E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>2043</v>
       </c>
@@ -7961,7 +8080,7 @@
         <v>8.3446428077986343E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>2044</v>
       </c>
@@ -7970,7 +8089,7 @@
         <v>8.165012532092597E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>2045</v>
       </c>
@@ -7979,7 +8098,7 @@
         <v>7.9892490529281768E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>2046</v>
       </c>
@@ -7988,7 +8107,7 @@
         <v>7.8172691320236562E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>2047</v>
       </c>
@@ -7997,7 +8116,7 @@
         <v>7.6489913229194281E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>2048</v>
       </c>
@@ -8006,7 +8125,7 @@
         <v>7.4843359324064856E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>2049</v>
       </c>
@@ -8015,7 +8134,7 @@
         <v>7.3232249827852106E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>2050</v>
       </c>
@@ -8024,7 +8143,7 @@
         <v>7.165582174936605E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>2051</v>
       </c>
@@ -8033,7 +8152,7 @@
         <v>7.0113328521884594E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>2052</v>
       </c>
@@ -8042,7 +8161,7 @@
         <v>6.8604039649593537E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>2053</v>
       </c>
@@ -8051,7 +8170,7 @@
         <v>6.7127240361637516E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>2054</v>
       </c>
@@ -8060,7 +8179,7 @@
         <v>6.5682231273617928E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>2055</v>
       </c>
@@ -8069,7 +8188,7 @@
         <v>6.4268328056377624E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>2056</v>
       </c>
@@ -8078,7 +8197,7 @@
         <v>6.2884861111915477E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>2057</v>
       </c>
@@ -8087,7 +8206,7 @@
         <v>6.1531175256277375E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>2058</v>
       </c>
@@ -8096,7 +8215,7 @@
         <v>6.0206629409273363E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>2059</v>
       </c>
@@ -8105,7 +8224,7 @@
         <v>5.8910596290874133E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>2060</v>
       </c>
